--- a/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_RMSEP.xlsx
@@ -19,12 +19,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Pretraitement</t>
   </si>
   <si>
     <t>RMSEP_glo</t>
+  </si>
+  <si>
+    <t>LV0_RMSEP</t>
   </si>
   <si>
     <t>LV1_RMSEP</t>
@@ -214,7 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,13 +233,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -246,12 +242,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -263,49 +274,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -605,14 +579,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,2448 +639,2589 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>23.523280079108531</v>
+        <v>23.567285294731651</v>
       </c>
       <c r="C2">
-        <v>28.235884643082969</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D2">
-        <v>23.672955976203511</v>
-      </c>
-      <c r="E2">
-        <v>22.70349680144351</v>
+        <v>28.267498759707909</v>
+      </c>
+      <c r="E2" s="2">
+        <v>23.673176014179141</v>
       </c>
       <c r="F2">
-        <v>22.34215321173674</v>
+        <v>22.70276806560225</v>
       </c>
       <c r="G2">
-        <v>22.788981232668299</v>
+        <v>22.322390132012359</v>
       </c>
       <c r="H2">
-        <v>22.01613419008957</v>
+        <v>22.71823606405389</v>
       </c>
       <c r="I2">
-        <v>21.87665409879363</v>
+        <v>21.98228615874125</v>
       </c>
       <c r="J2">
-        <v>22.614575556184199</v>
+        <v>21.813904525642759</v>
       </c>
       <c r="K2">
-        <v>22.13346124854786</v>
+        <v>22.501283821994999</v>
       </c>
       <c r="L2">
-        <v>22.674944664897371</v>
+        <v>22.062816814509912</v>
       </c>
       <c r="M2">
-        <v>23.024279835582441</v>
+        <v>22.608096770265099</v>
       </c>
       <c r="N2">
-        <v>24.315003547105889</v>
+        <v>22.963732432764651</v>
       </c>
       <c r="O2">
-        <v>25.868683973556209</v>
+        <v>24.106412655835559</v>
       </c>
       <c r="P2">
-        <v>27.1540162185714</v>
+        <v>25.784225556080951</v>
       </c>
       <c r="Q2">
-        <v>27.875836666159419</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>26.993972321183911</v>
+      </c>
+      <c r="R2">
+        <v>27.718481820630409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>23.230464861758769</v>
+        <v>23.411066204271911</v>
       </c>
       <c r="C3">
-        <v>26.77163659733105</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D3">
-        <v>23.15453111585439</v>
-      </c>
-      <c r="E3">
-        <v>23.484213371442081</v>
+        <v>26.724912573470661</v>
+      </c>
+      <c r="E3" s="2">
+        <v>23.171589420962121</v>
       </c>
       <c r="F3">
-        <v>24.645061628542951</v>
+        <v>23.51589811072288</v>
       </c>
       <c r="G3">
-        <v>23.94879108401139</v>
+        <v>24.61318468386234</v>
       </c>
       <c r="H3">
-        <v>23.84369488374551</v>
+        <v>23.81082634172661</v>
       </c>
       <c r="I3">
-        <v>25.0948620880073</v>
+        <v>23.725469334273829</v>
       </c>
       <c r="J3">
-        <v>25.411968876306371</v>
+        <v>25.045048720849991</v>
       </c>
       <c r="K3">
-        <v>26.55126026085987</v>
+        <v>25.38556983417693</v>
       </c>
       <c r="L3">
-        <v>26.985529967284489</v>
+        <v>26.612924691587821</v>
       </c>
       <c r="M3">
-        <v>27.554821124706031</v>
+        <v>27.11969846902954</v>
       </c>
       <c r="N3">
-        <v>28.5597594019452</v>
+        <v>27.705763437146022</v>
       </c>
       <c r="O3">
-        <v>29.225258990302471</v>
+        <v>28.738029573970721</v>
       </c>
       <c r="P3">
-        <v>29.275009791349689</v>
+        <v>29.518351802618081</v>
       </c>
       <c r="Q3">
-        <v>28.952329475762781</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>29.52691046327622</v>
+      </c>
+      <c r="R3">
+        <v>29.16732144444364</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>24.061058914565621</v>
+        <v>23.9509857776108</v>
       </c>
       <c r="C4">
-        <v>27.748633521791771</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D4">
-        <v>23.987639112358519</v>
-      </c>
-      <c r="E4">
-        <v>23.746649530756851</v>
+        <v>27.726749558465212</v>
+      </c>
+      <c r="E4" s="2">
+        <v>23.97203223237533</v>
       </c>
       <c r="F4">
-        <v>23.391377710141349</v>
+        <v>23.724946314039659</v>
       </c>
       <c r="G4">
-        <v>23.12597526234298</v>
+        <v>23.422170502405109</v>
       </c>
       <c r="H4">
-        <v>21.961036692859281</v>
+        <v>23.1817341618396</v>
       </c>
       <c r="I4">
-        <v>21.900652160488981</v>
+        <v>21.9685952593209</v>
       </c>
       <c r="J4">
-        <v>22.21173884012795</v>
+        <v>21.894106166314319</v>
       </c>
       <c r="K4">
-        <v>22.891681629354778</v>
+        <v>22.256062094377612</v>
       </c>
       <c r="L4">
-        <v>23.475767793995399</v>
+        <v>22.844579498172731</v>
       </c>
       <c r="M4">
-        <v>24.446314090265691</v>
+        <v>23.707096441186579</v>
       </c>
       <c r="N4">
-        <v>25.813372489473011</v>
+        <v>24.61286275543549</v>
       </c>
       <c r="O4">
-        <v>27.14265634657151</v>
+        <v>26.1142658091476</v>
       </c>
       <c r="P4">
-        <v>27.98550552845553</v>
+        <v>27.38054313196384</v>
       </c>
       <c r="Q4">
-        <v>28.750974165456441</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>28.24692850354861</v>
+      </c>
+      <c r="R4">
+        <v>28.937532961799342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>23.399199388689489</v>
+        <v>23.41399364632338</v>
       </c>
       <c r="C5">
-        <v>23.408415081415171</v>
-      </c>
-      <c r="D5">
-        <v>23.20535946173845</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D5" s="2">
+        <v>23.373791312282929</v>
       </c>
       <c r="E5">
-        <v>22.966623387821841</v>
+        <v>23.176280870180591</v>
       </c>
       <c r="F5">
-        <v>23.104616835660192</v>
+        <v>22.968111233395021</v>
       </c>
       <c r="G5">
-        <v>22.877521402147231</v>
+        <v>23.13043341213967</v>
       </c>
       <c r="H5">
-        <v>22.872632414615691</v>
+        <v>22.913371086333981</v>
       </c>
       <c r="I5">
-        <v>23.397618979827399</v>
+        <v>22.965100138874948</v>
       </c>
       <c r="J5">
-        <v>24.50469042188254</v>
+        <v>23.448462259298729</v>
       </c>
       <c r="K5">
-        <v>26.45041051942292</v>
+        <v>24.556579898522749</v>
       </c>
       <c r="L5">
-        <v>27.45461545426998</v>
+        <v>26.47576564375025</v>
       </c>
       <c r="M5">
-        <v>28.100012592639299</v>
+        <v>27.425794300555371</v>
       </c>
       <c r="N5">
-        <v>28.283896038961839</v>
+        <v>28.17978000369887</v>
       </c>
       <c r="O5">
-        <v>28.074371665965099</v>
+        <v>28.226268972561218</v>
       </c>
       <c r="P5">
-        <v>28.1000668118071</v>
+        <v>28.083115849710889</v>
       </c>
       <c r="Q5">
-        <v>28.27196985544073</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>28.114762972836871</v>
+      </c>
+      <c r="R5">
+        <v>28.247083212479641</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>23.532140273497031</v>
+        <v>23.509649766306101</v>
       </c>
       <c r="C6">
-        <v>23.452674926139629</v>
-      </c>
-      <c r="D6">
-        <v>23.251926749235519</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D6" s="2">
+        <v>23.41602059388223</v>
       </c>
       <c r="E6">
-        <v>22.917763969977589</v>
+        <v>23.215648208082289</v>
       </c>
       <c r="F6">
-        <v>22.824516205905979</v>
+        <v>22.894731633902449</v>
       </c>
       <c r="G6">
-        <v>22.182106172844328</v>
+        <v>22.741150244542819</v>
       </c>
       <c r="H6">
-        <v>22.434411418759879</v>
+        <v>22.131958669124959</v>
       </c>
       <c r="I6">
-        <v>23.269125182180971</v>
+        <v>22.352038197305848</v>
       </c>
       <c r="J6">
-        <v>23.921989031628211</v>
+        <v>23.108825775830159</v>
       </c>
       <c r="K6">
-        <v>24.876396362276409</v>
+        <v>23.815969260716709</v>
       </c>
       <c r="L6">
-        <v>25.2784294457845</v>
+        <v>24.721942539222042</v>
       </c>
       <c r="M6">
-        <v>26.070660693027349</v>
+        <v>25.14003393720542</v>
       </c>
       <c r="N6">
-        <v>26.630213944951681</v>
+        <v>25.899220834274651</v>
       </c>
       <c r="O6">
-        <v>27.01380604825621</v>
+        <v>26.359972412008851</v>
       </c>
       <c r="P6">
-        <v>27.147775634543041</v>
+        <v>26.910966763454169</v>
       </c>
       <c r="Q6">
-        <v>27.406818581570921</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <v>27.066279657423319</v>
+      </c>
+      <c r="R6">
+        <v>27.267593306954399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>23.562360099243179</v>
+        <v>23.51137169440312</v>
       </c>
       <c r="C7">
-        <v>27.64753149684703</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D7">
-        <v>23.653158205191989</v>
-      </c>
-      <c r="E7">
-        <v>22.267883441395622</v>
+        <v>27.583896956891842</v>
+      </c>
+      <c r="E7" s="2">
+        <v>23.57587456277837</v>
       </c>
       <c r="F7">
-        <v>21.981000347484422</v>
+        <v>22.15609926988931</v>
       </c>
       <c r="G7">
-        <v>22.032741678754871</v>
+        <v>21.884440108442199</v>
       </c>
       <c r="H7">
-        <v>21.706598430148091</v>
+        <v>21.9257221638616</v>
       </c>
       <c r="I7">
-        <v>22.060196637094698</v>
+        <v>21.591167714411</v>
       </c>
       <c r="J7">
-        <v>22.05521530211977</v>
+        <v>22.04697423257247</v>
       </c>
       <c r="K7">
-        <v>22.444106507014141</v>
+        <v>22.005165836465761</v>
       </c>
       <c r="L7">
-        <v>23.252280420374461</v>
+        <v>22.34237433187257</v>
       </c>
       <c r="M7">
-        <v>23.97491539487849</v>
+        <v>23.095372258907041</v>
       </c>
       <c r="N7">
-        <v>25.71728849633341</v>
+        <v>23.885319708823509</v>
       </c>
       <c r="O7">
-        <v>26.811198069942041</v>
+        <v>25.626217766159581</v>
       </c>
       <c r="P7">
-        <v>28.08904752322313</v>
+        <v>26.713713901601832</v>
       </c>
       <c r="Q7">
-        <v>28.87151953256863</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>27.874455815008371</v>
+      </c>
+      <c r="R7">
+        <v>28.724205127650361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>23.609136809212831</v>
+        <v>23.567168759988931</v>
       </c>
       <c r="C8">
-        <v>25.792195662558349</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D8">
-        <v>23.717933345945958</v>
-      </c>
-      <c r="E8">
-        <v>22.234396802454</v>
+        <v>25.777024658523839</v>
+      </c>
+      <c r="E8" s="2">
+        <v>23.72539024128006</v>
       </c>
       <c r="F8">
-        <v>21.78972822971026</v>
+        <v>22.24211924070605</v>
       </c>
       <c r="G8">
-        <v>21.661806471339951</v>
+        <v>21.847728656810339</v>
       </c>
       <c r="H8">
-        <v>22.09186766831202</v>
+        <v>21.649847624575589</v>
       </c>
       <c r="I8">
-        <v>22.09227716289508</v>
+        <v>21.963556260309659</v>
       </c>
       <c r="J8">
-        <v>22.795768727112911</v>
+        <v>22.02555081255365</v>
       </c>
       <c r="K8">
-        <v>23.997403863039889</v>
+        <v>22.82636517922391</v>
       </c>
       <c r="L8">
-        <v>24.499032590391831</v>
+        <v>24.010844195259541</v>
       </c>
       <c r="M8">
-        <v>25.047184873171691</v>
+        <v>24.618562446061631</v>
       </c>
       <c r="N8">
-        <v>26.035594457014859</v>
+        <v>25.187909543278671</v>
       </c>
       <c r="O8">
-        <v>27.681194339757202</v>
+        <v>26.106865175903021</v>
       </c>
       <c r="P8">
-        <v>28.898204040810452</v>
+        <v>27.73141529377023</v>
       </c>
       <c r="Q8">
-        <v>29.607931148982871</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>28.86994884256719</v>
+      </c>
+      <c r="R8">
+        <v>29.62983024672905</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>23.436497430314908</v>
+        <v>23.507181728828272</v>
       </c>
       <c r="C9">
-        <v>25.74620330429337</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D9">
-        <v>23.68558784272761</v>
-      </c>
-      <c r="E9">
-        <v>22.202737721723331</v>
+        <v>25.780873039179699</v>
+      </c>
+      <c r="E9" s="2">
+        <v>23.711766516978809</v>
       </c>
       <c r="F9">
-        <v>21.791735583520051</v>
+        <v>22.261507825811201</v>
       </c>
       <c r="G9">
-        <v>21.519363419600609</v>
+        <v>21.86504982648637</v>
       </c>
       <c r="H9">
-        <v>21.799635987348061</v>
+        <v>21.624994575545049</v>
       </c>
       <c r="I9">
-        <v>21.7088525662945</v>
+        <v>21.970745388677109</v>
       </c>
       <c r="J9">
-        <v>21.931328544711359</v>
+        <v>21.909552656251591</v>
       </c>
       <c r="K9">
-        <v>22.499331436099791</v>
+        <v>22.132551484064521</v>
       </c>
       <c r="L9">
-        <v>22.89949261267007</v>
+        <v>22.759261999931091</v>
       </c>
       <c r="M9">
-        <v>22.9204060493038</v>
+        <v>23.022390271402259</v>
       </c>
       <c r="N9">
-        <v>23.16857739641457</v>
+        <v>23.04120291066582</v>
       </c>
       <c r="O9">
-        <v>24.043687392066431</v>
+        <v>23.30971497746604</v>
       </c>
       <c r="P9">
-        <v>24.475355007215668</v>
+        <v>24.188661028109291</v>
       </c>
       <c r="Q9">
-        <v>24.972808730209309</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>24.617536262065979</v>
+      </c>
+      <c r="R9">
+        <v>25.14271088541231</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>23.517619078031231</v>
+        <v>23.50961095524648</v>
       </c>
       <c r="C10">
-        <v>25.813569840952951</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D10">
-        <v>23.739701008361411</v>
-      </c>
-      <c r="E10">
-        <v>22.23710796113485</v>
+        <v>25.76746325714014</v>
+      </c>
+      <c r="E10" s="2">
+        <v>23.690558218456481</v>
       </c>
       <c r="F10">
-        <v>21.802396606907902</v>
+        <v>22.22432906260401</v>
       </c>
       <c r="G10">
-        <v>21.609333479598138</v>
+        <v>21.794762439524501</v>
       </c>
       <c r="H10">
-        <v>21.864362514709029</v>
+        <v>21.485871767201349</v>
       </c>
       <c r="I10">
-        <v>21.762981686600291</v>
+        <v>21.83733576952396</v>
       </c>
       <c r="J10">
-        <v>21.962917681390621</v>
+        <v>21.759687357574059</v>
       </c>
       <c r="K10">
-        <v>22.50986884171687</v>
+        <v>21.964633312786621</v>
       </c>
       <c r="L10">
-        <v>22.814865965751579</v>
+        <v>22.448524446588991</v>
       </c>
       <c r="M10">
-        <v>22.834934172638519</v>
+        <v>22.809080825195409</v>
       </c>
       <c r="N10">
-        <v>23.126331623251691</v>
+        <v>22.86628602337554</v>
       </c>
       <c r="O10">
-        <v>23.980854116233999</v>
+        <v>23.16514085175131</v>
       </c>
       <c r="P10">
-        <v>24.471552005811152</v>
+        <v>24.042881219001639</v>
       </c>
       <c r="Q10">
-        <v>25.065775773875998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <v>24.54451085894604</v>
+      </c>
+      <c r="R10">
+        <v>25.223255649369609</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
-        <v>23.616851831476769</v>
+        <v>23.545509825346048</v>
       </c>
       <c r="C11">
-        <v>25.787624504329191</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D11">
-        <v>23.7127364791655</v>
-      </c>
-      <c r="E11">
-        <v>22.263236407214041</v>
+        <v>25.800672963590269</v>
+      </c>
+      <c r="E11" s="2">
+        <v>23.743457437546478</v>
       </c>
       <c r="F11">
-        <v>21.864014539292249</v>
+        <v>22.246146719482191</v>
       </c>
       <c r="G11">
-        <v>21.65130367918756</v>
+        <v>21.867934069540599</v>
       </c>
       <c r="H11">
-        <v>21.96410196983279</v>
+        <v>21.634008321754511</v>
       </c>
       <c r="I11">
-        <v>21.90232383362509</v>
+        <v>21.918199144726231</v>
       </c>
       <c r="J11">
-        <v>22.08865445176815</v>
+        <v>21.90773866951848</v>
       </c>
       <c r="K11">
-        <v>22.59616056635917</v>
+        <v>22.157013261228869</v>
       </c>
       <c r="L11">
-        <v>22.670891942599269</v>
+        <v>22.689786975157318</v>
       </c>
       <c r="M11">
-        <v>22.600178958210321</v>
+        <v>22.78875516804894</v>
       </c>
       <c r="N11">
-        <v>22.79307630109491</v>
+        <v>22.68245264991511</v>
       </c>
       <c r="O11">
-        <v>23.70478781673182</v>
+        <v>22.946922767712621</v>
       </c>
       <c r="P11">
-        <v>24.378176155038961</v>
+        <v>23.83229250759025</v>
       </c>
       <c r="Q11">
-        <v>24.827074523896691</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>24.468906257658901</v>
+      </c>
+      <c r="R11">
+        <v>24.927510626153179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>22.864604321495669</v>
+        <v>22.87493238486654</v>
       </c>
       <c r="C12">
-        <v>22.870348029941781</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D12">
-        <v>22.586494709575529</v>
+        <v>22.877742597994779</v>
       </c>
       <c r="E12">
-        <v>22.331380623499779</v>
+        <v>22.584810748038091</v>
       </c>
       <c r="F12">
-        <v>22.28507245080305</v>
+        <v>22.377731558046989</v>
       </c>
       <c r="G12">
-        <v>22.23863071440115</v>
+        <v>22.368866877915501</v>
       </c>
       <c r="H12">
-        <v>22.274151659216749</v>
+        <v>22.23760753052456</v>
       </c>
       <c r="I12">
-        <v>22.870442978572552</v>
+        <v>22.30407863084201</v>
       </c>
       <c r="J12">
-        <v>24.054546965775931</v>
+        <v>22.91124125450926</v>
       </c>
       <c r="K12">
-        <v>25.741680576766932</v>
+        <v>24.073254179664978</v>
       </c>
       <c r="L12">
-        <v>27.133961071509091</v>
+        <v>25.730729711592719</v>
       </c>
       <c r="M12">
-        <v>28.678734524230741</v>
+        <v>27.1070628028274</v>
       </c>
       <c r="N12">
-        <v>29.223947574824461</v>
+        <v>28.648447281070322</v>
       </c>
       <c r="O12">
-        <v>29.062280237665181</v>
+        <v>29.254360704945491</v>
       </c>
       <c r="P12">
-        <v>29.00747745378402</v>
+        <v>29.125329110791331</v>
       </c>
       <c r="Q12">
-        <v>29.551584903898171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>29.103145288913272</v>
+      </c>
+      <c r="R12">
+        <v>29.652562036967389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>23.005138430198489</v>
+        <v>22.98627449854812</v>
       </c>
       <c r="C13">
-        <v>23.005138430198489</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D13">
-        <v>23.059543447094441</v>
+        <v>22.98627449854812</v>
       </c>
       <c r="E13">
-        <v>22.635846724081681</v>
+        <v>23.047077801440281</v>
       </c>
       <c r="F13">
-        <v>22.252129740370471</v>
+        <v>22.75286390626956</v>
       </c>
       <c r="G13">
-        <v>23.473346429547281</v>
+        <v>22.32342761790424</v>
       </c>
       <c r="H13">
-        <v>23.89069491431086</v>
+        <v>23.60337886037038</v>
       </c>
       <c r="I13">
-        <v>23.968462588243479</v>
+        <v>24.032047102606409</v>
       </c>
       <c r="J13">
-        <v>24.510831266122359</v>
+        <v>24.12296771861584</v>
       </c>
       <c r="K13">
-        <v>26.40768463483915</v>
+        <v>24.511025650578521</v>
       </c>
       <c r="L13">
-        <v>28.042185256170139</v>
+        <v>26.361024330791661</v>
       </c>
       <c r="M13">
-        <v>28.565170124594509</v>
+        <v>28.02112207377137</v>
       </c>
       <c r="N13">
-        <v>28.66936838043317</v>
+        <v>28.524709951816899</v>
       </c>
       <c r="O13">
-        <v>29.190071220752479</v>
+        <v>28.67746607429514</v>
       </c>
       <c r="P13">
-        <v>29.503889953657541</v>
+        <v>29.184356448681619</v>
       </c>
       <c r="Q13">
-        <v>30.285225064148069</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>29.394843610445001</v>
+      </c>
+      <c r="R13">
+        <v>30.16273160921309</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>23.368891513560229</v>
+        <v>23.37592386889958</v>
       </c>
       <c r="C14">
-        <v>27.568098547548569</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D14">
-        <v>23.594411528920119</v>
+        <v>27.580909856222171</v>
       </c>
       <c r="E14">
-        <v>22.185418903122901</v>
+        <v>23.612301633453662</v>
       </c>
       <c r="F14">
-        <v>21.926416750390249</v>
+        <v>22.16732154400653</v>
       </c>
       <c r="G14">
-        <v>21.94446442978672</v>
+        <v>21.872275423064369</v>
       </c>
       <c r="H14">
-        <v>21.515714335145379</v>
+        <v>21.847467934827112</v>
       </c>
       <c r="I14">
-        <v>21.815187733594399</v>
+        <v>21.645680555919451</v>
       </c>
       <c r="J14">
-        <v>21.696426324158999</v>
+        <v>21.85440307111341</v>
       </c>
       <c r="K14">
-        <v>21.80888500868118</v>
+        <v>21.75838680798099</v>
       </c>
       <c r="L14">
-        <v>22.172308694664611</v>
+        <v>21.878008261010219</v>
       </c>
       <c r="M14">
-        <v>22.27882361233268</v>
+        <v>22.272143926219272</v>
       </c>
       <c r="N14">
-        <v>22.875906073817688</v>
+        <v>22.404643660009839</v>
       </c>
       <c r="O14">
-        <v>23.640664564414671</v>
+        <v>22.965253699858462</v>
       </c>
       <c r="P14">
-        <v>24.605070002935101</v>
+        <v>23.691439718910789</v>
       </c>
       <c r="Q14">
-        <v>25.79262804322877</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <v>24.772375182356392</v>
+      </c>
+      <c r="R14">
+        <v>25.930756281528659</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>23.51564610709265</v>
+        <v>23.363504665915169</v>
       </c>
       <c r="C15">
-        <v>27.622650081135951</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D15">
-        <v>23.682788839200491</v>
+        <v>27.604305387432561</v>
       </c>
       <c r="E15">
-        <v>22.282598043381281</v>
+        <v>23.6075602472194</v>
       </c>
       <c r="F15">
-        <v>21.98334125967758</v>
+        <v>22.16410548878731</v>
       </c>
       <c r="G15">
-        <v>22.03634869553219</v>
+        <v>21.905331343958309</v>
       </c>
       <c r="H15">
-        <v>21.60088787565828</v>
+        <v>21.898163718007488</v>
       </c>
       <c r="I15">
-        <v>21.987478952497622</v>
+        <v>21.51937055943359</v>
       </c>
       <c r="J15">
-        <v>21.823006260208331</v>
+        <v>21.789736322980961</v>
       </c>
       <c r="K15">
-        <v>21.88736189464689</v>
+        <v>21.671266246070601</v>
       </c>
       <c r="L15">
-        <v>22.31090667456963</v>
+        <v>21.811276140744749</v>
       </c>
       <c r="M15">
-        <v>22.463900734098001</v>
+        <v>22.162002056386559</v>
       </c>
       <c r="N15">
-        <v>23.047449792987631</v>
+        <v>22.276036673470319</v>
       </c>
       <c r="O15">
-        <v>23.984290296217829</v>
+        <v>22.936813295364111</v>
       </c>
       <c r="P15">
-        <v>24.677419332835122</v>
+        <v>23.817646495758162</v>
       </c>
       <c r="Q15">
-        <v>24.99297764642343</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <v>24.474844413764959</v>
+      </c>
+      <c r="R15">
+        <v>24.91908263245007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>23.465428377211001</v>
+        <v>23.40275714289789</v>
       </c>
       <c r="C16">
-        <v>27.60264648774627</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D16">
-        <v>23.629894635676461</v>
+        <v>27.574477021890509</v>
       </c>
       <c r="E16">
-        <v>22.26780588982551</v>
+        <v>23.590421774981571</v>
       </c>
       <c r="F16">
-        <v>21.993217092262029</v>
+        <v>22.199195044994749</v>
       </c>
       <c r="G16">
-        <v>22.031844184206889</v>
+        <v>21.936176669402929</v>
       </c>
       <c r="H16">
-        <v>21.664078430392699</v>
+        <v>21.957669522522909</v>
       </c>
       <c r="I16">
-        <v>21.935136917159419</v>
+        <v>21.604531314861269</v>
       </c>
       <c r="J16">
-        <v>21.839228359757609</v>
+        <v>21.861382759720041</v>
       </c>
       <c r="K16">
-        <v>21.97819467682648</v>
+        <v>21.71798568899511</v>
       </c>
       <c r="L16">
-        <v>22.394171093909009</v>
+        <v>21.813510936691969</v>
       </c>
       <c r="M16">
-        <v>22.462846809283398</v>
+        <v>22.18142832918587</v>
       </c>
       <c r="N16">
-        <v>23.3063783554189</v>
+        <v>22.34218393972915</v>
       </c>
       <c r="O16">
-        <v>24.335327912447749</v>
+        <v>23.216639475786561</v>
       </c>
       <c r="P16">
-        <v>25.095820505933439</v>
+        <v>24.304153354820599</v>
       </c>
       <c r="Q16">
-        <v>25.253614956095092</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25.059595946523292</v>
+      </c>
+      <c r="R16">
+        <v>25.296303071038</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>23.365646562094529</v>
+        <v>23.468391786644599</v>
       </c>
       <c r="C17">
-        <v>27.585332702177151</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D17">
-        <v>23.595860699450562</v>
+        <v>27.605228238445751</v>
       </c>
       <c r="E17">
-        <v>22.16097463422425</v>
+        <v>23.645850909548301</v>
       </c>
       <c r="F17">
-        <v>21.893784345173081</v>
+        <v>22.282116818243509</v>
       </c>
       <c r="G17">
-        <v>21.88967425565432</v>
-      </c>
-      <c r="H17" s="2">
-        <v>21.514221181793491</v>
+        <v>22.033314930443719</v>
+      </c>
+      <c r="H17">
+        <v>22.05592183569491</v>
       </c>
       <c r="I17">
-        <v>21.791427890447459</v>
+        <v>21.657420283201819</v>
       </c>
       <c r="J17">
-        <v>21.670116015100209</v>
+        <v>21.953249559419131</v>
       </c>
       <c r="K17">
-        <v>21.787235134601222</v>
+        <v>21.795791043902341</v>
       </c>
       <c r="L17">
-        <v>22.20623208587952</v>
+        <v>21.873989759440889</v>
       </c>
       <c r="M17">
-        <v>22.285105288341111</v>
+        <v>22.254703791388671</v>
       </c>
       <c r="N17">
-        <v>23.283449903400172</v>
+        <v>22.29308153453951</v>
       </c>
       <c r="O17">
-        <v>24.28004828540746</v>
+        <v>23.259183864278981</v>
       </c>
       <c r="P17">
-        <v>25.105075937859279</v>
+        <v>24.231732937855401</v>
       </c>
       <c r="Q17">
-        <v>25.33659297183711</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25.047858459818141</v>
+      </c>
+      <c r="R17">
+        <v>25.25891826105606</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18">
-        <v>22.87803122533446</v>
+        <v>22.895668541049378</v>
       </c>
       <c r="C18">
-        <v>22.880649452481201</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D18">
-        <v>22.704819621049442</v>
+        <v>22.902840986732961</v>
       </c>
       <c r="E18">
-        <v>22.490330365913351</v>
+        <v>22.64570061612298</v>
       </c>
       <c r="F18">
-        <v>22.57738750826373</v>
+        <v>22.548383486289602</v>
       </c>
       <c r="G18">
-        <v>22.27104870608575</v>
+        <v>22.68788475038356</v>
       </c>
       <c r="H18">
-        <v>22.683151653470059</v>
+        <v>22.304708652427468</v>
       </c>
       <c r="I18">
-        <v>23.011901142800632</v>
+        <v>22.781156418619702</v>
       </c>
       <c r="J18">
-        <v>24.11006209778882</v>
+        <v>23.08036938149505</v>
       </c>
       <c r="K18">
-        <v>25.625707366939409</v>
+        <v>24.06327416170862</v>
       </c>
       <c r="L18">
-        <v>27.064031849034851</v>
+        <v>25.57344542808254</v>
       </c>
       <c r="M18">
-        <v>28.26437912262173</v>
+        <v>26.942536950611519</v>
       </c>
       <c r="N18">
-        <v>28.705561859360369</v>
+        <v>28.104054919761701</v>
       </c>
       <c r="O18">
-        <v>28.65122314747752</v>
+        <v>28.552169076795401</v>
       </c>
       <c r="P18">
-        <v>28.569932536602671</v>
+        <v>28.5514164035542</v>
       </c>
       <c r="Q18">
-        <v>28.501557534090551</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>28.445672136825429</v>
+      </c>
+      <c r="R18">
+        <v>28.37163500189391</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>23.018764453770899</v>
+        <v>22.913528625594161</v>
       </c>
       <c r="C19">
-        <v>22.991821994060601</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D19">
-        <v>22.70014656582816</v>
+        <v>22.955050682869139</v>
       </c>
       <c r="E19">
-        <v>22.338531110125</v>
+        <v>22.674238454993851</v>
       </c>
       <c r="F19">
-        <v>22.178161202045441</v>
+        <v>22.325907963424921</v>
       </c>
       <c r="G19">
-        <v>21.61431947201649</v>
+        <v>22.089790568325711</v>
       </c>
       <c r="H19">
-        <v>22.31646877913942</v>
+        <v>21.593357866065659</v>
       </c>
       <c r="I19">
-        <v>22.321262406242369</v>
+        <v>22.281327459871221</v>
       </c>
       <c r="J19">
-        <v>23.117747223416711</v>
+        <v>22.308137361929969</v>
       </c>
       <c r="K19">
-        <v>24.078445985490031</v>
+        <v>23.00535996840668</v>
       </c>
       <c r="L19">
-        <v>25.038888370146442</v>
+        <v>23.966396381818171</v>
       </c>
       <c r="M19">
-        <v>26.010122208116972</v>
+        <v>24.967212505410551</v>
       </c>
       <c r="N19">
-        <v>26.61339480626523</v>
+        <v>25.93181406000603</v>
       </c>
       <c r="O19">
-        <v>27.202075365486369</v>
+        <v>26.536534789754342</v>
       </c>
       <c r="P19">
-        <v>27.553012640098849</v>
+        <v>27.146713705415419</v>
       </c>
       <c r="Q19">
-        <v>27.952014588206008</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>27.458972748689028</v>
+      </c>
+      <c r="R19">
+        <v>27.828171721799819</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20">
-        <v>22.932161733943751</v>
+        <v>22.977987940191131</v>
       </c>
       <c r="C20">
-        <v>22.97317735190693</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D20">
-        <v>22.617397482425449</v>
+        <v>22.98811556750217</v>
       </c>
       <c r="E20">
-        <v>22.03423996803879</v>
+        <v>22.58263402055384</v>
       </c>
       <c r="F20">
-        <v>22.019374718536479</v>
+        <v>21.973959203179</v>
       </c>
       <c r="G20">
-        <v>21.627767061729958</v>
+        <v>21.893171171392741</v>
       </c>
       <c r="H20">
-        <v>21.61109015774678</v>
+        <v>21.54786726116237</v>
       </c>
       <c r="I20">
-        <v>22.15127733181404</v>
+        <v>21.525985508238769</v>
       </c>
       <c r="J20">
-        <v>23.020191285147931</v>
+        <v>21.989511284954521</v>
       </c>
       <c r="K20">
-        <v>23.648632693332111</v>
+        <v>22.853058562862842</v>
       </c>
       <c r="L20">
-        <v>23.933053687811629</v>
+        <v>23.526837762315989</v>
       </c>
       <c r="M20">
-        <v>24.77741299463705</v>
+        <v>23.885102194814579</v>
       </c>
       <c r="N20">
-        <v>25.40032170166894</v>
+        <v>24.580389765980449</v>
       </c>
       <c r="O20">
-        <v>25.524168139481219</v>
+        <v>25.24603064253921</v>
       </c>
       <c r="P20">
-        <v>26.155159386072459</v>
+        <v>25.414520478483809</v>
       </c>
       <c r="Q20">
-        <v>26.71553216359634</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>26.08620671189578</v>
+      </c>
+      <c r="R20">
+        <v>26.724052127090321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21">
-        <v>23.391568382239651</v>
+        <v>23.350428733708341</v>
       </c>
       <c r="C21">
-        <v>26.76093889777475</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D21">
-        <v>23.22263535862011</v>
+        <v>26.722516745880359</v>
       </c>
       <c r="E21">
-        <v>23.544074030701889</v>
+        <v>23.195619789440631</v>
       </c>
       <c r="F21">
-        <v>24.619438736364291</v>
+        <v>23.542424766842171</v>
       </c>
       <c r="G21">
-        <v>23.746538546734708</v>
+        <v>24.649623775235678</v>
       </c>
       <c r="H21">
-        <v>24.02767741573043</v>
+        <v>23.7567745610773</v>
       </c>
       <c r="I21">
-        <v>25.565289555591821</v>
+        <v>23.918531248805671</v>
       </c>
       <c r="J21">
-        <v>27.369575104209861</v>
+        <v>25.559344412737801</v>
       </c>
       <c r="K21">
-        <v>27.793472806266632</v>
+        <v>27.117049470124439</v>
       </c>
       <c r="L21">
-        <v>28.617327616761109</v>
+        <v>27.609674046624921</v>
       </c>
       <c r="M21">
-        <v>28.880684556754382</v>
+        <v>28.427384528309091</v>
       </c>
       <c r="N21">
-        <v>29.124549368734609</v>
+        <v>28.71514160911698</v>
       </c>
       <c r="O21">
-        <v>29.105428350449181</v>
+        <v>29.024836862819349</v>
       </c>
       <c r="P21">
-        <v>29.003975452215421</v>
+        <v>28.98039770540295</v>
       </c>
       <c r="Q21">
-        <v>29.467619776930661</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>28.854107568441119</v>
+      </c>
+      <c r="R21">
+        <v>29.269441273356492</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>23.418140305762009</v>
+        <v>23.388384424628281</v>
       </c>
       <c r="C22">
-        <v>26.84462134640679</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D22">
-        <v>23.316851016482939</v>
+        <v>26.797144236695441</v>
       </c>
       <c r="E22">
-        <v>23.62376838863781</v>
+        <v>23.240206403918929</v>
       </c>
       <c r="F22">
-        <v>24.71180313490731</v>
+        <v>23.52574871959354</v>
       </c>
       <c r="G22">
-        <v>23.821892430162961</v>
+        <v>24.64870050232598</v>
       </c>
       <c r="H22">
-        <v>23.83470139018732</v>
+        <v>23.811800945261179</v>
       </c>
       <c r="I22">
-        <v>25.69686649436181</v>
+        <v>23.734815784438851</v>
       </c>
       <c r="J22">
-        <v>27.313746292382209</v>
+        <v>25.542477703036951</v>
       </c>
       <c r="K22">
-        <v>28.09890354450572</v>
+        <v>27.062217703020899</v>
       </c>
       <c r="L22">
-        <v>28.53329291157393</v>
+        <v>27.850192724137202</v>
       </c>
       <c r="M22">
-        <v>29.061193290190261</v>
+        <v>28.1778098614882</v>
       </c>
       <c r="N22">
-        <v>29.16716015706055</v>
+        <v>28.666004042184401</v>
       </c>
       <c r="O22">
-        <v>28.89739496673231</v>
+        <v>28.75030732456138</v>
       </c>
       <c r="P22">
-        <v>28.85157891096484</v>
+        <v>28.480839182166392</v>
       </c>
       <c r="Q22">
-        <v>29.588558015565599</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>28.3743683022775</v>
+      </c>
+      <c r="R22">
+        <v>29.22006081714882</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23">
-        <v>23.061674715757121</v>
+        <v>23.085787055029758</v>
       </c>
       <c r="C23">
-        <v>23.061674715757121</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D23">
-        <v>23.142799826214251</v>
+        <v>23.085787055029758</v>
       </c>
       <c r="E23">
-        <v>23.692144513253599</v>
+        <v>23.120254215300811</v>
       </c>
       <c r="F23">
-        <v>23.032814335749279</v>
+        <v>23.67247167773035</v>
       </c>
       <c r="G23">
-        <v>24.678436387365711</v>
+        <v>23.084954145372429</v>
       </c>
       <c r="H23">
-        <v>26.098324163841941</v>
+        <v>24.676975739039051</v>
       </c>
       <c r="I23">
-        <v>27.64583254747135</v>
+        <v>25.84291347777274</v>
       </c>
       <c r="J23">
-        <v>28.084917735675539</v>
+        <v>27.514641546883809</v>
       </c>
       <c r="K23">
-        <v>27.898422816612019</v>
+        <v>27.937589991814342</v>
       </c>
       <c r="L23">
-        <v>28.802253799294132</v>
+        <v>27.71144256993038</v>
       </c>
       <c r="M23">
-        <v>29.351688654333671</v>
+        <v>28.679336399675201</v>
       </c>
       <c r="N23">
-        <v>29.856858273643169</v>
+        <v>29.25205419839434</v>
       </c>
       <c r="O23">
-        <v>30.478238714847649</v>
+        <v>29.665519879720009</v>
       </c>
       <c r="P23">
-        <v>30.651187495785329</v>
+        <v>30.294382479351071</v>
       </c>
       <c r="Q23">
-        <v>31.225720849568471</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>30.534475991016851</v>
+      </c>
+      <c r="R23">
+        <v>31.134334330864881</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24">
-        <v>33.880396596281543</v>
+        <v>33.892769234453297</v>
       </c>
       <c r="C24">
-        <v>33.859681293468128</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D24">
-        <v>33.001370963539529</v>
+        <v>33.824850987447007</v>
       </c>
       <c r="E24">
-        <v>32.383251252882879</v>
+        <v>33.010923739069433</v>
       </c>
       <c r="F24">
-        <v>33.079212025566292</v>
+        <v>32.455265764754927</v>
       </c>
       <c r="G24">
-        <v>35.468016758949503</v>
+        <v>33.073526466382397</v>
       </c>
       <c r="H24">
-        <v>35.212229311789443</v>
+        <v>35.356711781383048</v>
       </c>
       <c r="I24">
-        <v>36.529341493899949</v>
+        <v>35.08595918085657</v>
       </c>
       <c r="J24">
-        <v>38.516987368735592</v>
+        <v>36.283117112930732</v>
       </c>
       <c r="K24">
-        <v>40.570956244886112</v>
+        <v>38.13379281391812</v>
       </c>
       <c r="L24">
-        <v>42.097040374781592</v>
+        <v>40.275515824758067</v>
       </c>
       <c r="M24">
-        <v>42.070365576394813</v>
+        <v>41.645685616851402</v>
       </c>
       <c r="N24">
-        <v>41.882139537362903</v>
+        <v>41.701467277986687</v>
       </c>
       <c r="O24">
-        <v>41.241315901505267</v>
+        <v>41.686230172734319</v>
       </c>
       <c r="P24">
-        <v>40.783478944338377</v>
+        <v>40.789943347214567</v>
       </c>
       <c r="Q24">
-        <v>40.868776637385658</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <v>40.262321791947151</v>
+      </c>
+      <c r="R24">
+        <v>40.322515056952838</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25">
-        <v>34.610157147714041</v>
+        <v>34.552408292907607</v>
       </c>
       <c r="C25">
-        <v>34.506648122572777</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D25">
-        <v>34.153798085465937</v>
+        <v>34.430038395025129</v>
       </c>
       <c r="E25">
-        <v>34.100498491076451</v>
+        <v>33.964622854938668</v>
       </c>
       <c r="F25">
-        <v>33.652149668422823</v>
+        <v>33.871476751625799</v>
       </c>
       <c r="G25">
-        <v>33.858297769233758</v>
+        <v>33.526179815522433</v>
       </c>
       <c r="H25">
-        <v>35.914134588161787</v>
+        <v>33.759134919271908</v>
       </c>
       <c r="I25">
-        <v>38.00073689078588</v>
+        <v>35.735420374980841</v>
       </c>
       <c r="J25">
-        <v>40.603889076343968</v>
+        <v>37.918954345461252</v>
       </c>
       <c r="K25">
-        <v>43.116392350610617</v>
+        <v>40.333393195732818</v>
       </c>
       <c r="L25">
-        <v>44.95507042778825</v>
+        <v>42.819467585577463</v>
       </c>
       <c r="M25">
-        <v>46.766459273752012</v>
+        <v>44.705478654981277</v>
       </c>
       <c r="N25">
-        <v>48.405807631069202</v>
+        <v>46.688846446285119</v>
       </c>
       <c r="O25">
-        <v>49.438454168797918</v>
+        <v>48.537969149841267</v>
       </c>
       <c r="P25">
-        <v>50.559822317849203</v>
+        <v>49.536281643590762</v>
       </c>
       <c r="Q25">
-        <v>51.031482706546349</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <v>50.633393274680607</v>
+      </c>
+      <c r="R25">
+        <v>51.189897360868763</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>34.411064658838832</v>
+        <v>34.402134027824999</v>
       </c>
       <c r="C26">
-        <v>34.253884088879559</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D26">
-        <v>33.604663778785387</v>
+        <v>34.211853950345358</v>
       </c>
       <c r="E26">
-        <v>32.988195980684523</v>
+        <v>33.508394080031323</v>
       </c>
       <c r="F26">
-        <v>32.596128979388332</v>
+        <v>32.888418200084189</v>
       </c>
       <c r="G26">
-        <v>32.872374710858807</v>
+        <v>32.537870924819011</v>
       </c>
       <c r="H26">
-        <v>33.275566491886458</v>
+        <v>32.907428529858727</v>
       </c>
       <c r="I26">
-        <v>34.055193095699828</v>
+        <v>33.448003938787323</v>
       </c>
       <c r="J26">
-        <v>34.050393938674162</v>
+        <v>34.096346981961347</v>
       </c>
       <c r="K26">
-        <v>34.160391140566148</v>
+        <v>34.209064918976523</v>
       </c>
       <c r="L26">
-        <v>34.158307175401347</v>
+        <v>34.143323285091178</v>
       </c>
       <c r="M26">
-        <v>34.863070885069313</v>
+        <v>34.263148481815271</v>
       </c>
       <c r="N26">
-        <v>35.124737450168887</v>
+        <v>34.724672417583847</v>
       </c>
       <c r="O26">
-        <v>36.515410629109518</v>
+        <v>35.284255643712328</v>
       </c>
       <c r="P26">
-        <v>36.647440783410467</v>
+        <v>36.668152497001387</v>
       </c>
       <c r="Q26">
-        <v>37.29170422622564</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+        <v>36.767953020475467</v>
+      </c>
+      <c r="R26">
+        <v>37.488224664771167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27">
-        <v>34.947827344164438</v>
+        <v>35.047130941101031</v>
       </c>
       <c r="C27">
-        <v>34.702309820620407</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D27">
-        <v>34.029206837681123</v>
+        <v>34.752145599364781</v>
       </c>
       <c r="E27">
-        <v>33.018414397256556</v>
+        <v>34.109685022615523</v>
       </c>
       <c r="F27">
-        <v>32.007187884433073</v>
+        <v>33.001138259245479</v>
       </c>
       <c r="G27">
-        <v>32.708009554067687</v>
+        <v>32.068705753012637</v>
       </c>
       <c r="H27">
-        <v>33.948551444021888</v>
+        <v>32.747522464974018</v>
       </c>
       <c r="I27">
-        <v>34.383926889584579</v>
+        <v>34.072368851519691</v>
       </c>
       <c r="J27">
-        <v>34.761251596775629</v>
+        <v>34.557912769438502</v>
       </c>
       <c r="K27">
-        <v>35.019471452632423</v>
+        <v>34.964967828374178</v>
       </c>
       <c r="L27">
-        <v>35.307438670307818</v>
+        <v>35.247872441862079</v>
       </c>
       <c r="M27">
-        <v>35.741350944808893</v>
+        <v>35.410598725401833</v>
       </c>
       <c r="N27">
-        <v>36.94233727698213</v>
+        <v>35.837898547659179</v>
       </c>
       <c r="O27">
-        <v>37.829429330084729</v>
+        <v>36.982160985577188</v>
       </c>
       <c r="P27">
-        <v>39.467700709793903</v>
+        <v>37.861873541492301</v>
       </c>
       <c r="Q27">
-        <v>40.943324258510508</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+        <v>39.414876467334622</v>
+      </c>
+      <c r="R27">
+        <v>40.807439151777267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28">
-        <v>23.156159080695939</v>
+        <v>23.163462450724531</v>
       </c>
       <c r="C28">
-        <v>23.21198751870422</v>
-      </c>
-      <c r="D28">
-        <v>22.261254947654528</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D28" s="2">
+        <v>23.211250047975</v>
       </c>
       <c r="E28">
-        <v>22.97217649109481</v>
+        <v>22.266649396964439</v>
       </c>
       <c r="F28">
-        <v>22.37913163897635</v>
+        <v>22.954358059083329</v>
       </c>
       <c r="G28">
-        <v>22.477027227192451</v>
+        <v>22.418546285953759</v>
       </c>
       <c r="H28">
-        <v>22.281066625002321</v>
+        <v>22.5021189867511</v>
       </c>
       <c r="I28">
-        <v>22.795879881170219</v>
+        <v>22.341916664225</v>
       </c>
       <c r="J28">
-        <v>23.328440975129261</v>
+        <v>22.87339119311978</v>
       </c>
       <c r="K28">
-        <v>23.072917611240481</v>
+        <v>23.418316882235018</v>
       </c>
       <c r="L28">
-        <v>23.352907898075632</v>
+        <v>23.192855500835108</v>
       </c>
       <c r="M28">
-        <v>24.035047465497801</v>
+        <v>23.409089447304979</v>
       </c>
       <c r="N28">
-        <v>25.35269246077987</v>
+        <v>23.997050357392361</v>
       </c>
       <c r="O28">
-        <v>26.24945101685757</v>
+        <v>25.305218396851519</v>
       </c>
       <c r="P28">
-        <v>27.73236180672016</v>
+        <v>26.161685506728631</v>
       </c>
       <c r="Q28">
-        <v>29.110211960709201</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+        <v>27.599308430758018</v>
+      </c>
+      <c r="R28">
+        <v>28.96180006069379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29">
-        <v>23.171172958730281</v>
+        <v>23.0117541265165</v>
       </c>
       <c r="C29">
-        <v>23.12753933040868</v>
-      </c>
-      <c r="D29">
-        <v>22.190045102731499</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D29" s="2">
+        <v>23.081196173332469</v>
       </c>
       <c r="E29">
-        <v>22.925045962817329</v>
+        <v>22.151311774761311</v>
       </c>
       <c r="F29">
-        <v>22.388778760607721</v>
+        <v>22.88648850867639</v>
       </c>
       <c r="G29">
-        <v>22.756785192065319</v>
+        <v>22.330034188640688</v>
       </c>
       <c r="H29">
-        <v>23.46326325533656</v>
+        <v>22.671031290249338</v>
       </c>
       <c r="I29">
-        <v>24.309300728241389</v>
+        <v>23.30030888998348</v>
       </c>
       <c r="J29">
-        <v>24.00874394281583</v>
+        <v>24.164768841378681</v>
       </c>
       <c r="K29">
-        <v>24.09527381008672</v>
+        <v>23.819912606042369</v>
       </c>
       <c r="L29">
-        <v>23.664446154887791</v>
+        <v>24.04510538144357</v>
       </c>
       <c r="M29">
-        <v>24.175663809209841</v>
+        <v>23.673282220396889</v>
       </c>
       <c r="N29">
-        <v>24.95918367046432</v>
+        <v>24.351696426497121</v>
       </c>
       <c r="O29">
-        <v>26.21587549960298</v>
+        <v>25.200424336548569</v>
       </c>
       <c r="P29">
-        <v>27.071991910581289</v>
+        <v>26.445917718431211</v>
       </c>
       <c r="Q29">
-        <v>28.59635083383229</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>27.43292612242935</v>
+      </c>
+      <c r="R29">
+        <v>28.992427297876571</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>22.44508313541704</v>
+        <v>22.3788635713852</v>
       </c>
       <c r="C30">
-        <v>22.30237242905941</v>
-      </c>
-      <c r="D30">
-        <v>22.16757933955947</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D30" s="2">
+        <v>22.306285454222039</v>
       </c>
       <c r="E30">
-        <v>22.74935620672019</v>
+        <v>22.166945795337181</v>
       </c>
       <c r="F30">
-        <v>22.26396270725995</v>
+        <v>22.731589188084911</v>
       </c>
       <c r="G30">
-        <v>22.403720849498079</v>
+        <v>22.26643402070744</v>
       </c>
       <c r="H30">
-        <v>22.252596975372441</v>
+        <v>22.36034557879394</v>
       </c>
       <c r="I30">
-        <v>22.761121571608061</v>
+        <v>22.319105695827218</v>
       </c>
       <c r="J30">
-        <v>23.278582120512631</v>
+        <v>22.75581179723325</v>
       </c>
       <c r="K30">
-        <v>23.401354108320639</v>
+        <v>23.441997091037351</v>
       </c>
       <c r="L30">
-        <v>23.60278626968736</v>
+        <v>23.480336884308709</v>
       </c>
       <c r="M30">
-        <v>24.56653324126642</v>
+        <v>23.721537230454501</v>
       </c>
       <c r="N30">
-        <v>25.596185754708909</v>
+        <v>24.659934018729501</v>
       </c>
       <c r="O30">
-        <v>26.978689393343181</v>
+        <v>25.75651940085956</v>
       </c>
       <c r="P30">
-        <v>28.268604432263071</v>
+        <v>27.207807577571408</v>
       </c>
       <c r="Q30">
-        <v>30.55649029005221</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>28.521565737528949</v>
+      </c>
+      <c r="R30">
+        <v>30.78080843118617</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31">
-        <v>22.41854449906883</v>
+        <v>22.340127365159969</v>
       </c>
       <c r="C31">
-        <v>22.337116172689399</v>
-      </c>
-      <c r="D31">
-        <v>22.21356336021914</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D31" s="2">
+        <v>22.288008009199832</v>
       </c>
       <c r="E31">
-        <v>22.787575809031051</v>
+        <v>22.158638682610199</v>
       </c>
       <c r="F31">
-        <v>22.368490503775529</v>
+        <v>22.731085507962121</v>
       </c>
       <c r="G31">
-        <v>22.448240634809149</v>
+        <v>22.272919490822069</v>
       </c>
       <c r="H31">
-        <v>22.333818156770391</v>
+        <v>22.388180731271529</v>
       </c>
       <c r="I31">
-        <v>22.467294340483889</v>
+        <v>22.219158205326881</v>
       </c>
       <c r="J31">
-        <v>22.780483751190591</v>
+        <v>22.37487109147532</v>
       </c>
       <c r="K31">
-        <v>22.53666150946837</v>
+        <v>22.572682342576289</v>
       </c>
       <c r="L31">
-        <v>22.212359708923231</v>
+        <v>22.416888771883279</v>
       </c>
       <c r="M31">
-        <v>22.30314119172802</v>
+        <v>22.096676903239569</v>
       </c>
       <c r="N31">
-        <v>22.748275016572052</v>
+        <v>22.212693254531811</v>
       </c>
       <c r="O31">
-        <v>23.674743947503099</v>
+        <v>22.734196334988351</v>
       </c>
       <c r="P31">
-        <v>23.809160046989071</v>
+        <v>23.686895905412388</v>
       </c>
       <c r="Q31">
-        <v>25.748722791953529</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.776966137875728</v>
+      </c>
+      <c r="R31">
+        <v>25.77935041222706</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32">
-        <v>23.063080121630168</v>
+        <v>23.062868980475191</v>
       </c>
       <c r="C32">
-        <v>23.103413235734479</v>
-      </c>
-      <c r="D32">
-        <v>22.189967152247711</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D32" s="2">
+        <v>23.12003199874691</v>
       </c>
       <c r="E32">
-        <v>22.970745099466502</v>
+        <v>22.190026417136082</v>
       </c>
       <c r="F32">
-        <v>22.453518248458909</v>
+        <v>22.951141902359598</v>
       </c>
       <c r="G32">
-        <v>22.71989369627288</v>
+        <v>22.380062626919621</v>
       </c>
       <c r="H32">
-        <v>23.183761444362911</v>
+        <v>22.652854526024921</v>
       </c>
       <c r="I32">
-        <v>23.78097206584717</v>
+        <v>23.074485807820061</v>
       </c>
       <c r="J32">
-        <v>23.392801927223129</v>
+        <v>23.631752268694129</v>
       </c>
       <c r="K32">
-        <v>23.253090081473871</v>
+        <v>23.159276166781481</v>
       </c>
       <c r="L32">
-        <v>22.846992432892311</v>
+        <v>23.10546695830331</v>
       </c>
       <c r="M32">
-        <v>22.901115039751321</v>
+        <v>22.750098896695441</v>
       </c>
       <c r="N32">
-        <v>23.21400002851631</v>
+        <v>22.886575629816392</v>
       </c>
       <c r="O32">
-        <v>24.034585127770679</v>
+        <v>23.157637945966439</v>
       </c>
       <c r="P32">
-        <v>24.278979484558992</v>
+        <v>24.01316972756058</v>
       </c>
       <c r="Q32">
-        <v>25.23155002537969</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+        <v>24.30104148591743</v>
+      </c>
+      <c r="R32">
+        <v>25.272295774222702</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33">
-        <v>23.02223017128382</v>
+        <v>23.13871665756276</v>
       </c>
       <c r="C33">
-        <v>23.11190514564862</v>
-      </c>
-      <c r="D33">
-        <v>22.182482129650261</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D33" s="2">
+        <v>23.137928354373361</v>
       </c>
       <c r="E33">
-        <v>22.879719803021409</v>
+        <v>22.160160602654351</v>
       </c>
       <c r="F33">
-        <v>22.344733156289969</v>
+        <v>22.889835862765981</v>
       </c>
       <c r="G33">
-        <v>22.5973312493497</v>
+        <v>22.399514707440972</v>
       </c>
       <c r="H33">
-        <v>23.005961623480299</v>
+        <v>22.685731229775101</v>
       </c>
       <c r="I33">
-        <v>23.493914468268589</v>
+        <v>23.1795433636319</v>
       </c>
       <c r="J33">
-        <v>23.29724441048743</v>
+        <v>23.656668806044081</v>
       </c>
       <c r="K33">
-        <v>23.20732827912995</v>
+        <v>23.370479736917499</v>
       </c>
       <c r="L33">
-        <v>22.67616381399354</v>
+        <v>23.329617350977831</v>
       </c>
       <c r="M33">
-        <v>22.7606986470057</v>
+        <v>22.776989897908461</v>
       </c>
       <c r="N33">
-        <v>23.040479940135299</v>
+        <v>22.79048887458184</v>
       </c>
       <c r="O33">
-        <v>23.860982124672979</v>
+        <v>23.047676434639971</v>
       </c>
       <c r="P33">
-        <v>23.900858828141089</v>
+        <v>23.83420132566896</v>
       </c>
       <c r="Q33">
-        <v>24.903334184073959</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.970165505624859</v>
+      </c>
+      <c r="R33">
+        <v>24.906280324272341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>23.112168112509728</v>
+        <v>23.105959369936031</v>
       </c>
       <c r="C34">
-        <v>23.145108532338849</v>
-      </c>
-      <c r="D34">
-        <v>22.217275683338791</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D34" s="2">
+        <v>23.15927873301845</v>
       </c>
       <c r="E34">
-        <v>22.951102272638121</v>
+        <v>22.234376936940748</v>
       </c>
       <c r="F34">
-        <v>22.45210395943354</v>
+        <v>23.00780012775229</v>
       </c>
       <c r="G34">
-        <v>22.749996814558479</v>
+        <v>22.542754446499679</v>
       </c>
       <c r="H34">
-        <v>23.186943271673911</v>
+        <v>22.81185204439657</v>
       </c>
       <c r="I34">
-        <v>23.605834467820209</v>
+        <v>23.27043858822756</v>
       </c>
       <c r="J34">
-        <v>23.15037489752957</v>
+        <v>23.749706988854101</v>
       </c>
       <c r="K34">
-        <v>23.12306458527906</v>
+        <v>23.390005970871272</v>
       </c>
       <c r="L34">
-        <v>22.737437551666979</v>
+        <v>23.25688204082148</v>
       </c>
       <c r="M34">
-        <v>22.755536356048971</v>
+        <v>22.833895301465908</v>
       </c>
       <c r="N34">
-        <v>22.938724675366469</v>
+        <v>22.814749904382101</v>
       </c>
       <c r="O34">
-        <v>23.51372295341741</v>
+        <v>23.084673866401619</v>
       </c>
       <c r="P34">
-        <v>23.71641703743428</v>
+        <v>23.7178520249035</v>
       </c>
       <c r="Q34">
-        <v>24.502275067198969</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.834816718368991</v>
+      </c>
+      <c r="R34">
+        <v>24.643728224356931</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B35">
-        <v>23.052991381377961</v>
+        <v>23.078815924057771</v>
       </c>
       <c r="C35">
-        <v>23.101954420875369</v>
-      </c>
-      <c r="D35">
-        <v>22.14275161461315</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D35" s="2">
+        <v>23.137124159871959</v>
       </c>
       <c r="E35">
-        <v>22.87244662965869</v>
+        <v>22.169500492672231</v>
       </c>
       <c r="F35">
-        <v>22.307501107057941</v>
+        <v>22.880459533439812</v>
       </c>
       <c r="G35">
-        <v>22.596011038974641</v>
+        <v>22.385426794106799</v>
       </c>
       <c r="H35">
-        <v>22.981473355759618</v>
+        <v>22.69490848306846</v>
       </c>
       <c r="I35">
-        <v>23.414330538080101</v>
+        <v>23.22573114644624</v>
       </c>
       <c r="J35">
-        <v>23.0581948513905</v>
+        <v>23.68318734193733</v>
       </c>
       <c r="K35">
-        <v>23.178359994663921</v>
+        <v>23.330004409626181</v>
       </c>
       <c r="L35">
-        <v>22.667116831760151</v>
+        <v>23.34267337620437</v>
       </c>
       <c r="M35">
-        <v>22.72422904097882</v>
+        <v>22.822170380588769</v>
       </c>
       <c r="N35">
-        <v>22.776408380061682</v>
+        <v>22.863549337800009</v>
       </c>
       <c r="O35">
-        <v>23.38025664336552</v>
+        <v>22.922284851044751</v>
       </c>
       <c r="P35">
-        <v>23.447975932286951</v>
+        <v>23.498550082080879</v>
       </c>
       <c r="Q35">
-        <v>24.050506638852141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.598886633010341</v>
+      </c>
+      <c r="R35">
+        <v>24.199146071540479</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36">
-        <v>23.03588104218699</v>
+        <v>23.121949138326482</v>
       </c>
       <c r="C36">
-        <v>23.101313732247451</v>
-      </c>
-      <c r="D36">
-        <v>22.162777069402321</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D36" s="2">
+        <v>23.123017550362061</v>
       </c>
       <c r="E36">
-        <v>22.86271692416663</v>
+        <v>22.176105272933949</v>
       </c>
       <c r="F36">
-        <v>22.411318799869431</v>
+        <v>22.870742669042141</v>
       </c>
       <c r="G36">
-        <v>22.645357956009249</v>
+        <v>22.350147871499448</v>
       </c>
       <c r="H36">
-        <v>23.130997631624059</v>
+        <v>22.63715656955867</v>
       </c>
       <c r="I36">
-        <v>23.69785646443308</v>
+        <v>23.048183920390031</v>
       </c>
       <c r="J36">
-        <v>23.309279772836149</v>
+        <v>23.609571174613009</v>
       </c>
       <c r="K36">
-        <v>23.227247048907579</v>
+        <v>23.299449189778219</v>
       </c>
       <c r="L36">
-        <v>22.691312433219441</v>
+        <v>23.347697412367339</v>
       </c>
       <c r="M36">
-        <v>22.89272977885263</v>
+        <v>22.730021152173912</v>
       </c>
       <c r="N36">
-        <v>23.289572303646501</v>
+        <v>22.837817590751349</v>
       </c>
       <c r="O36">
-        <v>24.18010082065906</v>
+        <v>23.28060263935668</v>
       </c>
       <c r="P36">
-        <v>24.109131099010739</v>
+        <v>24.102900707410829</v>
       </c>
       <c r="Q36">
-        <v>24.801015292914151</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.997526427891259</v>
+      </c>
+      <c r="R36">
+        <v>24.82260732727487</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>22.978770231582061</v>
+        <v>23.120618530900622</v>
       </c>
       <c r="C37">
-        <v>23.07606413739439</v>
-      </c>
-      <c r="D37">
-        <v>22.12341647527786</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D37" s="2">
+        <v>23.10562317759819</v>
       </c>
       <c r="E37">
-        <v>22.765905648284939</v>
+        <v>22.1655537018177</v>
       </c>
       <c r="F37">
-        <v>22.30168963336984</v>
+        <v>22.871878489529301</v>
       </c>
       <c r="G37">
-        <v>22.59722830641492</v>
+        <v>22.358544653530959</v>
       </c>
       <c r="H37">
-        <v>23.038648105224219</v>
+        <v>22.630880584456879</v>
       </c>
       <c r="I37">
-        <v>23.583364579393471</v>
+        <v>23.084181373368398</v>
       </c>
       <c r="J37">
-        <v>23.216582173215748</v>
+        <v>23.608075279594321</v>
       </c>
       <c r="K37">
-        <v>23.08569820350727</v>
+        <v>23.22286666046919</v>
       </c>
       <c r="L37">
-        <v>22.50376272992299</v>
+        <v>23.170662474817519</v>
       </c>
       <c r="M37">
-        <v>22.71737494699207</v>
+        <v>22.602978441730119</v>
       </c>
       <c r="N37">
-        <v>23.109334048132951</v>
+        <v>22.797305913464619</v>
       </c>
       <c r="O37">
-        <v>23.7600587327846</v>
+        <v>23.072430137546199</v>
       </c>
       <c r="P37">
-        <v>23.680072546160321</v>
+        <v>23.774021456329741</v>
       </c>
       <c r="Q37">
-        <v>24.401436783676282</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.721682940968179</v>
+      </c>
+      <c r="R37">
+        <v>24.34633063832575</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>23.08424161500756</v>
+        <v>23.079331955717919</v>
       </c>
       <c r="C38">
-        <v>23.08101844277687</v>
-      </c>
-      <c r="D38">
-        <v>22.150186075740869</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D38" s="2">
+        <v>23.108305773972329</v>
       </c>
       <c r="E38">
-        <v>22.92425633818835</v>
+        <v>22.162481838614379</v>
       </c>
       <c r="F38">
-        <v>22.41699432672527</v>
+        <v>22.842132160710449</v>
       </c>
       <c r="G38">
-        <v>22.68669458424845</v>
+        <v>22.365118253981649</v>
       </c>
       <c r="H38">
-        <v>23.071681925403571</v>
+        <v>22.67165571101858</v>
       </c>
       <c r="I38">
-        <v>23.67165721044935</v>
+        <v>23.165165724137019</v>
       </c>
       <c r="J38">
-        <v>23.28640265114732</v>
+        <v>23.67417646404407</v>
       </c>
       <c r="K38">
-        <v>23.137984736337341</v>
+        <v>23.272304024036789</v>
       </c>
       <c r="L38">
-        <v>22.643777800451819</v>
+        <v>23.138300570887569</v>
       </c>
       <c r="M38">
-        <v>22.83727129227816</v>
+        <v>22.533904131052729</v>
       </c>
       <c r="N38">
-        <v>23.258146349532129</v>
+        <v>22.595436878454489</v>
       </c>
       <c r="O38">
-        <v>24.002031884865438</v>
+        <v>22.93918853301934</v>
       </c>
       <c r="P38">
-        <v>23.924782535980871</v>
+        <v>23.690189910579011</v>
       </c>
       <c r="Q38">
-        <v>24.599488471112199</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.532931852840559</v>
+      </c>
+      <c r="R38">
+        <v>24.19650719605491</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39">
-        <v>23.041525768523542</v>
+        <v>23.034499956042161</v>
       </c>
       <c r="C39">
-        <v>23.117914411029041</v>
-      </c>
-      <c r="D39">
-        <v>22.215380316080459</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D39" s="2">
+        <v>23.12791361923183</v>
       </c>
       <c r="E39">
-        <v>22.979767405480381</v>
+        <v>22.188188111773531</v>
       </c>
       <c r="F39">
-        <v>22.46267058331793</v>
+        <v>22.936982288375869</v>
       </c>
       <c r="G39">
-        <v>22.727818797610482</v>
+        <v>22.406561908741121</v>
       </c>
       <c r="H39">
-        <v>23.154490048388841</v>
+        <v>22.687666523834309</v>
       </c>
       <c r="I39">
-        <v>23.71932398436217</v>
+        <v>23.165177378747881</v>
       </c>
       <c r="J39">
-        <v>23.27426708571916</v>
+        <v>23.733413226924931</v>
       </c>
       <c r="K39">
-        <v>23.1954928342487</v>
+        <v>23.449400835814089</v>
       </c>
       <c r="L39">
-        <v>22.617599617846579</v>
+        <v>23.353018716034601</v>
       </c>
       <c r="M39">
-        <v>22.695718643493439</v>
+        <v>22.696508275382261</v>
       </c>
       <c r="N39">
-        <v>22.984760024880561</v>
+        <v>22.78542878379946</v>
       </c>
       <c r="O39">
-        <v>23.753056745667941</v>
+        <v>23.282946254653009</v>
       </c>
       <c r="P39">
-        <v>23.62504594256928</v>
+        <v>23.922762714771601</v>
       </c>
       <c r="Q39">
-        <v>24.227106262968171</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.851750378961011</v>
+      </c>
+      <c r="R39">
+        <v>24.432212608845049</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B40">
-        <v>23.028285348672011</v>
+        <v>23.06619191833267</v>
       </c>
       <c r="C40">
-        <v>23.057737032695329</v>
-      </c>
-      <c r="D40">
-        <v>22.114375828612399</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D40" s="2">
+        <v>23.088729718591559</v>
       </c>
       <c r="E40">
-        <v>22.76394541825734</v>
+        <v>22.176765161508701</v>
       </c>
       <c r="F40">
-        <v>22.29330453556042</v>
+        <v>23.023313167807409</v>
       </c>
       <c r="G40">
-        <v>22.552719436859739</v>
+        <v>22.47994624885424</v>
       </c>
       <c r="H40">
-        <v>23.0242863601318</v>
+        <v>22.744254812536859</v>
       </c>
       <c r="I40">
-        <v>23.573208214781889</v>
+        <v>23.175812498172071</v>
       </c>
       <c r="J40">
-        <v>23.107111756225969</v>
+        <v>23.646996560973069</v>
       </c>
       <c r="K40">
-        <v>23.11205870113659</v>
+        <v>23.265836178205461</v>
       </c>
       <c r="L40">
-        <v>22.604779508489919</v>
+        <v>23.336567838388</v>
       </c>
       <c r="M40">
-        <v>22.760588251315159</v>
+        <v>22.811683830249759</v>
       </c>
       <c r="N40">
-        <v>22.8244551714618</v>
+        <v>22.819052124430101</v>
       </c>
       <c r="O40">
-        <v>23.404546019610621</v>
+        <v>22.95547892555188</v>
       </c>
       <c r="P40">
-        <v>23.454735786926801</v>
+        <v>23.49642228606108</v>
       </c>
       <c r="Q40">
-        <v>23.936036285908699</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+        <v>23.55671237781463</v>
+      </c>
+      <c r="R40">
+        <v>23.962813030960771</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B41">
-        <v>22.14315058134191</v>
+        <v>22.14037477804478</v>
       </c>
       <c r="C41">
-        <v>22.13665759867564</v>
-      </c>
-      <c r="D41">
-        <v>22.136414064699139</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D41" s="2">
+        <v>22.134720271781749</v>
       </c>
       <c r="E41">
-        <v>22.16081337457944</v>
+        <v>22.127905090540601</v>
       </c>
       <c r="F41">
-        <v>22.233775205001859</v>
+        <v>22.131385384072431</v>
       </c>
       <c r="G41">
-        <v>23.139621886770598</v>
+        <v>22.215493053972718</v>
       </c>
       <c r="H41">
-        <v>23.979639843105321</v>
+        <v>23.09457222642294</v>
       </c>
       <c r="I41">
-        <v>23.474523399008849</v>
+        <v>23.938388877010961</v>
       </c>
       <c r="J41">
-        <v>23.738577678855041</v>
+        <v>23.46068210089738</v>
       </c>
       <c r="K41">
-        <v>24.123786101601009</v>
+        <v>23.80392016173149</v>
       </c>
       <c r="L41">
-        <v>25.04475938745902</v>
+        <v>24.26486679648913</v>
       </c>
       <c r="M41">
-        <v>26.255575815260158</v>
+        <v>25.13107953761703</v>
       </c>
       <c r="N41">
-        <v>27.664477209424771</v>
+        <v>26.25112215412064</v>
       </c>
       <c r="O41">
-        <v>29.612820113472541</v>
+        <v>27.707716330672461</v>
       </c>
       <c r="P41">
-        <v>30.817364567646749</v>
+        <v>29.791135741204961</v>
       </c>
       <c r="Q41">
-        <v>31.917196075503469</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+        <v>31.019847977445341</v>
+      </c>
+      <c r="R41">
+        <v>32.222963733551403</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B42">
-        <v>22.238512876987169</v>
+        <v>22.210476549271039</v>
       </c>
       <c r="C42">
-        <v>22.190659412176991</v>
-      </c>
-      <c r="D42">
-        <v>22.204524981645751</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D42" s="2">
+        <v>22.18121386875832</v>
       </c>
       <c r="E42">
-        <v>22.117842309549431</v>
+        <v>22.134500245393209</v>
       </c>
       <c r="F42">
-        <v>22.076982504252559</v>
+        <v>22.158563590047809</v>
       </c>
       <c r="G42">
-        <v>22.479981639585059</v>
+        <v>22.118311550663631</v>
       </c>
       <c r="H42">
-        <v>22.902624413557721</v>
+        <v>22.52741553963499</v>
       </c>
       <c r="I42">
-        <v>23.012052562406431</v>
+        <v>22.96138975221043</v>
       </c>
       <c r="J42">
-        <v>23.789469678131411</v>
+        <v>23.005404762469631</v>
       </c>
       <c r="K42">
-        <v>25.401738641297118</v>
+        <v>23.903691930746511</v>
       </c>
       <c r="L42">
-        <v>26.097843318679519</v>
+        <v>25.58378267508748</v>
       </c>
       <c r="M42">
-        <v>26.34535321360713</v>
+        <v>26.318226376317529</v>
       </c>
       <c r="N42">
-        <v>25.770021092458361</v>
+        <v>26.607223292450509</v>
       </c>
       <c r="O42">
-        <v>25.356195342166082</v>
+        <v>26.02433125938391</v>
       </c>
       <c r="P42">
-        <v>25.90688407338741</v>
+        <v>25.59304590346531</v>
       </c>
       <c r="Q42">
-        <v>26.344832976263788</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+        <v>26.150960596309051</v>
+      </c>
+      <c r="R42">
+        <v>26.66028130971468</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43">
-        <v>22.146985620535901</v>
+        <v>22.153459114107719</v>
       </c>
       <c r="C43">
-        <v>22.12649450392561</v>
-      </c>
-      <c r="D43">
-        <v>22.071712591725809</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D43" s="2">
+        <v>22.140646350376851</v>
       </c>
       <c r="E43">
-        <v>21.996325946235729</v>
+        <v>22.069410720928349</v>
       </c>
       <c r="F43">
-        <v>22.004920456775992</v>
+        <v>22.040414073089551</v>
       </c>
       <c r="G43">
-        <v>22.33045072644919</v>
+        <v>22.060503426201709</v>
       </c>
       <c r="H43">
-        <v>22.679589926528742</v>
+        <v>22.473458714452491</v>
       </c>
       <c r="I43">
-        <v>22.374350336163069</v>
+        <v>22.844871449384151</v>
       </c>
       <c r="J43">
-        <v>22.869415223642811</v>
+        <v>22.506722991016549</v>
       </c>
       <c r="K43">
-        <v>24.7269253122662</v>
+        <v>23.037675833855051</v>
       </c>
       <c r="L43">
-        <v>25.210003900981899</v>
+        <v>24.978171176229601</v>
       </c>
       <c r="M43">
-        <v>25.555452129387611</v>
+        <v>25.517412218001649</v>
       </c>
       <c r="N43">
-        <v>25.701162321944679</v>
+        <v>25.937715718441311</v>
       </c>
       <c r="O43">
-        <v>25.699712627572168</v>
+        <v>26.013978569334711</v>
       </c>
       <c r="P43">
-        <v>25.832839261755559</v>
+        <v>25.920767628401322</v>
       </c>
       <c r="Q43">
-        <v>26.800175732808391</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+        <v>25.937643797662449</v>
+      </c>
+      <c r="R43">
+        <v>26.98217519100028</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B44">
-        <v>23.44373526315816</v>
+        <v>23.475289450272079</v>
       </c>
       <c r="C44">
-        <v>23.230567686756231</v>
-      </c>
-      <c r="D44">
-        <v>23.401483303970451</v>
+        <v>36.778325263510503</v>
+      </c>
+      <c r="D44" s="2">
+        <v>23.237291851189411</v>
       </c>
       <c r="E44">
-        <v>23.804209423745771</v>
+        <v>23.372116853213068</v>
       </c>
       <c r="F44">
-        <v>22.86488834011325</v>
+        <v>23.769794812187431</v>
       </c>
       <c r="G44">
-        <v>22.366003136953701</v>
+        <v>22.800726405646309</v>
       </c>
       <c r="H44">
-        <v>23.12440308626833</v>
+        <v>22.381179621394761</v>
       </c>
       <c r="I44">
-        <v>24.087984927051121</v>
+        <v>23.067056036533771</v>
       </c>
       <c r="J44">
-        <v>24.954144611491209</v>
+        <v>24.023821357313281</v>
       </c>
       <c r="K44">
-        <v>25.491987318805819</v>
+        <v>24.938701912292309</v>
       </c>
       <c r="L44">
-        <v>26.08266562806126</v>
+        <v>25.458550613004029</v>
       </c>
       <c r="M44">
-        <v>27.148787920253149</v>
+        <v>26.02498598176609</v>
       </c>
       <c r="N44">
-        <v>28.86567027275219</v>
+        <v>27.076061632489949</v>
       </c>
       <c r="O44">
-        <v>30.919429972770018</v>
+        <v>28.84800957705643</v>
       </c>
       <c r="P44">
-        <v>32.933870817911021</v>
+        <v>31.048117970959101</v>
       </c>
       <c r="Q44">
-        <v>33.865021335080137</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+        <v>32.924221879598747</v>
+      </c>
+      <c r="R44">
+        <v>33.885228784444351</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B45">
-        <v>23.49791554483657</v>
+        <v>23.48137694321461</v>
       </c>
       <c r="C45">
-        <v>23.49791554483657</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D45">
-        <v>22.744549458167409</v>
+        <v>23.48137694321461</v>
       </c>
       <c r="E45">
-        <v>24.36117465696714</v>
+        <v>22.79085458081364</v>
       </c>
       <c r="F45">
-        <v>24.550848339197341</v>
+        <v>24.444536873452119</v>
       </c>
       <c r="G45">
-        <v>24.321595776797139</v>
+        <v>24.631518633595238</v>
       </c>
       <c r="H45">
-        <v>25.600693638087179</v>
+        <v>24.268756917305829</v>
       </c>
       <c r="I45">
-        <v>25.989085665192921</v>
+        <v>25.38047490515908</v>
       </c>
       <c r="J45">
-        <v>26.215810523410301</v>
+        <v>25.70574013255672</v>
       </c>
       <c r="K45">
-        <v>26.89128212969328</v>
+        <v>26.026620540133891</v>
       </c>
       <c r="L45">
-        <v>27.651526508685158</v>
+        <v>26.71069233759685</v>
       </c>
       <c r="M45">
-        <v>28.955286649977161</v>
+        <v>27.429773933397751</v>
       </c>
       <c r="N45">
-        <v>31.047343740347671</v>
+        <v>28.70740351692519</v>
       </c>
       <c r="O45">
-        <v>31.821957448703369</v>
+        <v>30.738712048828159</v>
       </c>
       <c r="P45">
-        <v>32.590889137445259</v>
+        <v>31.53593629873653</v>
       </c>
       <c r="Q45">
-        <v>33.191534642755308</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+        <v>32.410079960364293</v>
+      </c>
+      <c r="R45">
+        <v>33.017744157005268</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B46">
-        <v>22.808604477905291</v>
+        <v>22.798919668199861</v>
       </c>
       <c r="C46">
-        <v>26.730415671941032</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D46">
-        <v>22.80082724107233</v>
-      </c>
-      <c r="E46">
-        <v>23.92861110763382</v>
+        <v>26.708765672529019</v>
+      </c>
+      <c r="E46" s="2">
+        <v>22.775768706961301</v>
       </c>
       <c r="F46">
-        <v>25.341304966814839</v>
+        <v>23.870788732580358</v>
       </c>
       <c r="G46">
-        <v>24.735303196862699</v>
+        <v>25.307411509349201</v>
       </c>
       <c r="H46">
-        <v>24.215671910308671</v>
+        <v>24.795876393602121</v>
       </c>
       <c r="I46">
-        <v>24.72507556056993</v>
+        <v>24.214033259838779</v>
       </c>
       <c r="J46">
-        <v>26.35244660431778</v>
+        <v>24.71201627251088</v>
       </c>
       <c r="K46">
-        <v>28.128118464518369</v>
+        <v>26.41247652760341</v>
       </c>
       <c r="L46">
-        <v>29.235356805472652</v>
+        <v>28.024583041745231</v>
       </c>
       <c r="M46">
-        <v>30.214395557889599</v>
+        <v>29.121157804746979</v>
       </c>
       <c r="N46">
-        <v>30.761674871126761</v>
+        <v>30.15964936035741</v>
       </c>
       <c r="O46">
-        <v>31.400129299884949</v>
+        <v>30.644856638157972</v>
       </c>
       <c r="P46">
-        <v>32.42973056682203</v>
+        <v>31.176424245856769</v>
       </c>
       <c r="Q46">
-        <v>33.498223026165682</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+        <v>32.170679616360168</v>
+      </c>
+      <c r="R46">
+        <v>33.139741880308627</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B47">
-        <v>22.654771991275741</v>
+        <v>22.68759852640321</v>
       </c>
       <c r="C47">
-        <v>22.654771991275741</v>
+        <v>36.778325263510503</v>
       </c>
       <c r="D47">
-        <v>23.044515484478829</v>
+        <v>22.687598526403221</v>
       </c>
       <c r="E47">
-        <v>23.42492833152825</v>
+        <v>23.125797059178812</v>
       </c>
       <c r="F47">
-        <v>23.212833791264831</v>
+        <v>23.489124532847619</v>
       </c>
       <c r="G47">
-        <v>24.390912735426831</v>
+        <v>23.233899592958711</v>
       </c>
       <c r="H47">
-        <v>24.583419535774251</v>
+        <v>24.335401725174439</v>
       </c>
       <c r="I47">
-        <v>25.174814780551749</v>
+        <v>24.479720303008889</v>
       </c>
       <c r="J47">
-        <v>25.684074679608411</v>
+        <v>25.084873979295171</v>
       </c>
       <c r="K47">
-        <v>26.67135329127105</v>
+        <v>25.66625676063763</v>
       </c>
       <c r="L47">
-        <v>27.994460571858099</v>
+        <v>26.623985492304289</v>
       </c>
       <c r="M47">
-        <v>29.476823225487969</v>
+        <v>28.020076758863809</v>
       </c>
       <c r="N47">
-        <v>30.504929856885141</v>
+        <v>29.495048445414071</v>
       </c>
       <c r="O47">
-        <v>30.863334327558981</v>
+        <v>30.493431291058631</v>
       </c>
       <c r="P47">
-        <v>30.876560689846869</v>
+        <v>30.88837615192768</v>
       </c>
       <c r="Q47">
-        <v>31.25619777866893</v>
+        <v>30.963411252419469</v>
+      </c>
+      <c r="R47">
+        <v>31.363552726914278</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q16 C18:Q47 C17:G17 I17:Q17">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="C2:R47">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3115,9 +3231,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_RMSEP.xlsx
@@ -1,223 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\X13.cis.beta.carotene\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV0_RMSEP</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -250,50 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -335,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -367,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -402,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -578,2660 +350,2539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>23.567285294731651</v>
+        <v>23.47936179982776</v>
       </c>
       <c r="C2">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D2">
-        <v>28.267498759707909</v>
-      </c>
-      <c r="E2" s="2">
-        <v>23.673176014179141</v>
+        <v>28.25677527384965</v>
+      </c>
+      <c r="E2">
+        <v>23.62393146363803</v>
       </c>
       <c r="F2">
-        <v>22.70276806560225</v>
+        <v>22.70884395372683</v>
       </c>
       <c r="G2">
-        <v>22.322390132012359</v>
+        <v>22.37350123445112</v>
       </c>
       <c r="H2">
-        <v>22.71823606405389</v>
+        <v>22.7656038839328</v>
       </c>
       <c r="I2">
-        <v>21.98228615874125</v>
+        <v>22.05782140378277</v>
       </c>
       <c r="J2">
-        <v>21.813904525642759</v>
+        <v>21.92155975146008</v>
       </c>
       <c r="K2">
-        <v>22.501283821994999</v>
+        <v>22.55024015281616</v>
       </c>
       <c r="L2">
-        <v>22.062816814509912</v>
+        <v>22.24582072836179</v>
       </c>
       <c r="M2">
-        <v>22.608096770265099</v>
+        <v>22.80961847129263</v>
       </c>
       <c r="N2">
-        <v>22.963732432764651</v>
+        <v>23.13085951550166</v>
       </c>
       <c r="O2">
-        <v>24.106412655835559</v>
+        <v>24.39420199430904</v>
       </c>
       <c r="P2">
-        <v>25.784225556080951</v>
+        <v>26.00661440017483</v>
       </c>
       <c r="Q2">
-        <v>26.993972321183911</v>
+        <v>27.38000470279729</v>
       </c>
       <c r="R2">
-        <v>27.718481820630409</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
+        <v>27.99177357246779</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>23.411066204271911</v>
+        <v>23.2717955775616</v>
       </c>
       <c r="C3">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D3">
-        <v>26.724912573470661</v>
-      </c>
-      <c r="E3" s="2">
-        <v>23.171589420962121</v>
+        <v>26.73229248942049</v>
+      </c>
+      <c r="E3">
+        <v>23.1301234718599</v>
       </c>
       <c r="F3">
-        <v>23.51589811072288</v>
+        <v>23.47972326849572</v>
       </c>
       <c r="G3">
-        <v>24.61318468386234</v>
+        <v>24.66771866951647</v>
       </c>
       <c r="H3">
-        <v>23.81082634172661</v>
+        <v>23.82910875232461</v>
       </c>
       <c r="I3">
-        <v>23.725469334273829</v>
+        <v>23.83094093948123</v>
       </c>
       <c r="J3">
-        <v>25.045048720849991</v>
+        <v>25.01781663408177</v>
       </c>
       <c r="K3">
-        <v>25.38556983417693</v>
+        <v>25.4716648375746</v>
       </c>
       <c r="L3">
-        <v>26.612924691587821</v>
+        <v>26.68624568951991</v>
       </c>
       <c r="M3">
-        <v>27.11969846902954</v>
+        <v>27.14791857375612</v>
       </c>
       <c r="N3">
-        <v>27.705763437146022</v>
+        <v>27.78449469665567</v>
       </c>
       <c r="O3">
-        <v>28.738029573970721</v>
+        <v>28.80245054738698</v>
       </c>
       <c r="P3">
-        <v>29.518351802618081</v>
+        <v>29.50270845883072</v>
       </c>
       <c r="Q3">
-        <v>29.52691046327622</v>
+        <v>29.53242163429784</v>
       </c>
       <c r="R3">
-        <v>29.16732144444364</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
+        <v>29.11799223486617</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>23.9509857776108</v>
+        <v>24.05317834941806</v>
       </c>
       <c r="C4">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D4">
-        <v>27.726749558465212</v>
-      </c>
-      <c r="E4" s="2">
-        <v>23.97203223237533</v>
+        <v>27.71270193078872</v>
+      </c>
+      <c r="E4">
+        <v>23.95900755715674</v>
       </c>
       <c r="F4">
-        <v>23.724946314039659</v>
+        <v>23.68152186631388</v>
       </c>
       <c r="G4">
-        <v>23.422170502405109</v>
+        <v>23.34775001382525</v>
       </c>
       <c r="H4">
-        <v>23.1817341618396</v>
+        <v>23.04064602824906</v>
       </c>
       <c r="I4">
-        <v>21.9685952593209</v>
+        <v>21.96183929905626</v>
       </c>
       <c r="J4">
-        <v>21.894106166314319</v>
+        <v>21.88309525990694</v>
       </c>
       <c r="K4">
-        <v>22.256062094377612</v>
+        <v>22.19946555421401</v>
       </c>
       <c r="L4">
-        <v>22.844579498172731</v>
+        <v>22.74839691191801</v>
       </c>
       <c r="M4">
-        <v>23.707096441186579</v>
+        <v>23.483740310076</v>
       </c>
       <c r="N4">
-        <v>24.61286275543549</v>
+        <v>24.32671634569665</v>
       </c>
       <c r="O4">
-        <v>26.1142658091476</v>
+        <v>25.84163939444025</v>
       </c>
       <c r="P4">
-        <v>27.38054313196384</v>
+        <v>27.07427264268907</v>
       </c>
       <c r="Q4">
-        <v>28.24692850354861</v>
+        <v>27.92001816288029</v>
       </c>
       <c r="R4">
-        <v>28.937532961799342</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
+        <v>28.73813408029118</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>23.41399364632338</v>
+        <v>23.36070687700532</v>
       </c>
       <c r="C5">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D5" s="2">
-        <v>23.373791312282929</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D5">
+        <v>23.31581082693482</v>
       </c>
       <c r="E5">
-        <v>23.176280870180591</v>
+        <v>23.09558476159108</v>
       </c>
       <c r="F5">
-        <v>22.968111233395021</v>
+        <v>22.91363443450608</v>
       </c>
       <c r="G5">
-        <v>23.13043341213967</v>
+        <v>23.02380749117621</v>
       </c>
       <c r="H5">
-        <v>22.913371086333981</v>
+        <v>22.79068374320356</v>
       </c>
       <c r="I5">
-        <v>22.965100138874948</v>
+        <v>22.84600379731672</v>
       </c>
       <c r="J5">
-        <v>23.448462259298729</v>
+        <v>23.35436707169353</v>
       </c>
       <c r="K5">
-        <v>24.556579898522749</v>
+        <v>24.54551568034869</v>
       </c>
       <c r="L5">
-        <v>26.47576564375025</v>
+        <v>26.41901902010221</v>
       </c>
       <c r="M5">
-        <v>27.425794300555371</v>
+        <v>27.37039749816571</v>
       </c>
       <c r="N5">
-        <v>28.17978000369887</v>
+        <v>28.17331415445262</v>
       </c>
       <c r="O5">
-        <v>28.226268972561218</v>
+        <v>28.26906889631009</v>
       </c>
       <c r="P5">
-        <v>28.083115849710889</v>
+        <v>28.10907982282071</v>
       </c>
       <c r="Q5">
-        <v>28.114762972836871</v>
+        <v>28.05355015124112</v>
       </c>
       <c r="R5">
-        <v>28.247083212479641</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
+        <v>28.08766662340168</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>23.509649766306101</v>
+        <v>23.54483530858528</v>
       </c>
       <c r="C6">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D6" s="2">
-        <v>23.41602059388223</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D6">
+        <v>23.43250244036427</v>
       </c>
       <c r="E6">
-        <v>23.215648208082289</v>
+        <v>23.22781912041497</v>
       </c>
       <c r="F6">
-        <v>22.894731633902449</v>
+        <v>22.92846559019471</v>
       </c>
       <c r="G6">
-        <v>22.741150244542819</v>
+        <v>22.78362780411015</v>
       </c>
       <c r="H6">
-        <v>22.131958669124959</v>
+        <v>22.19011519674126</v>
       </c>
       <c r="I6">
-        <v>22.352038197305848</v>
+        <v>22.38370731565275</v>
       </c>
       <c r="J6">
-        <v>23.108825775830159</v>
+        <v>23.16055306545173</v>
       </c>
       <c r="K6">
-        <v>23.815969260716709</v>
+        <v>23.90285760486574</v>
       </c>
       <c r="L6">
-        <v>24.721942539222042</v>
+        <v>24.74372692490482</v>
       </c>
       <c r="M6">
-        <v>25.14003393720542</v>
+        <v>25.19797872222351</v>
       </c>
       <c r="N6">
-        <v>25.899220834274651</v>
+        <v>26.02795492257625</v>
       </c>
       <c r="O6">
-        <v>26.359972412008851</v>
+        <v>26.50531677819384</v>
       </c>
       <c r="P6">
-        <v>26.910966763454169</v>
+        <v>26.92223277679762</v>
       </c>
       <c r="Q6">
-        <v>27.066279657423319</v>
+        <v>27.0170524531357</v>
       </c>
       <c r="R6">
-        <v>27.267593306954399</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
+        <v>27.31603019904911</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>23.51137169440312</v>
+        <v>23.39097559023731</v>
       </c>
       <c r="C7">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D7">
-        <v>27.583896956891842</v>
-      </c>
-      <c r="E7" s="2">
-        <v>23.57587456277837</v>
+        <v>27.65982932196518</v>
+      </c>
+      <c r="E7">
+        <v>23.6194372408333</v>
       </c>
       <c r="F7">
-        <v>22.15609926988931</v>
+        <v>22.18998494112573</v>
       </c>
       <c r="G7">
-        <v>21.884440108442199</v>
+        <v>21.94308674972849</v>
       </c>
       <c r="H7">
-        <v>21.9257221638616</v>
+        <v>21.92256028117234</v>
       </c>
       <c r="I7">
-        <v>21.591167714411</v>
+        <v>21.64511187879291</v>
       </c>
       <c r="J7">
-        <v>22.04697423257247</v>
+        <v>21.93565590148425</v>
       </c>
       <c r="K7">
-        <v>22.005165836465761</v>
+        <v>21.89675551583464</v>
       </c>
       <c r="L7">
-        <v>22.34237433187257</v>
+        <v>22.3623168596387</v>
       </c>
       <c r="M7">
-        <v>23.095372258907041</v>
+        <v>23.06116408055109</v>
       </c>
       <c r="N7">
-        <v>23.885319708823509</v>
+        <v>23.77279513112846</v>
       </c>
       <c r="O7">
-        <v>25.626217766159581</v>
+        <v>25.36415868254067</v>
       </c>
       <c r="P7">
-        <v>26.713713901601832</v>
+        <v>26.50750293588183</v>
       </c>
       <c r="Q7">
-        <v>27.874455815008371</v>
+        <v>27.71924527517762</v>
       </c>
       <c r="R7">
-        <v>28.724205127650361</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
+        <v>28.40603324638889</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>23.567168759988931</v>
+        <v>23.53393140592127</v>
       </c>
       <c r="C8">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D8">
-        <v>25.777024658523839</v>
-      </c>
-      <c r="E8" s="2">
-        <v>23.72539024128006</v>
+        <v>25.78138123984557</v>
+      </c>
+      <c r="E8">
+        <v>23.71224410704146</v>
       </c>
       <c r="F8">
-        <v>22.24211924070605</v>
+        <v>22.24928182432465</v>
       </c>
       <c r="G8">
-        <v>21.847728656810339</v>
+        <v>21.90182965176314</v>
       </c>
       <c r="H8">
-        <v>21.649847624575589</v>
+        <v>21.67890324724541</v>
       </c>
       <c r="I8">
-        <v>21.963556260309659</v>
+        <v>22.17979856559915</v>
       </c>
       <c r="J8">
-        <v>22.02555081255365</v>
+        <v>22.22556759793047</v>
       </c>
       <c r="K8">
-        <v>22.82636517922391</v>
+        <v>23.09431545939564</v>
       </c>
       <c r="L8">
-        <v>24.010844195259541</v>
+        <v>24.35021333916427</v>
       </c>
       <c r="M8">
-        <v>24.618562446061631</v>
+        <v>24.98238500557315</v>
       </c>
       <c r="N8">
-        <v>25.187909543278671</v>
+        <v>25.47480798269329</v>
       </c>
       <c r="O8">
-        <v>26.106865175903021</v>
+        <v>26.43581042765867</v>
       </c>
       <c r="P8">
-        <v>27.73141529377023</v>
+        <v>28.06582590484436</v>
       </c>
       <c r="Q8">
-        <v>28.86994884256719</v>
+        <v>29.21190612474481</v>
       </c>
       <c r="R8">
-        <v>29.62983024672905</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
+        <v>29.90236329152732</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>23.507181728828272</v>
+        <v>23.52718521722961</v>
       </c>
       <c r="C9">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D9">
-        <v>25.780873039179699</v>
-      </c>
-      <c r="E9" s="2">
-        <v>23.711766516978809</v>
+        <v>25.81549343942005</v>
+      </c>
+      <c r="E9">
+        <v>23.78134148248057</v>
       </c>
       <c r="F9">
-        <v>22.261507825811201</v>
+        <v>22.31708793475688</v>
       </c>
       <c r="G9">
-        <v>21.86504982648637</v>
+        <v>21.90666932858417</v>
       </c>
       <c r="H9">
-        <v>21.624994575545049</v>
+        <v>21.58081863083466</v>
       </c>
       <c r="I9">
-        <v>21.970745388677109</v>
+        <v>21.94283543883008</v>
       </c>
       <c r="J9">
-        <v>21.909552656251591</v>
+        <v>21.88133166841511</v>
       </c>
       <c r="K9">
-        <v>22.132551484064521</v>
+        <v>22.12179571661925</v>
       </c>
       <c r="L9">
-        <v>22.759261999931091</v>
+        <v>22.7545906890131</v>
       </c>
       <c r="M9">
-        <v>23.022390271402259</v>
+        <v>23.15439044426712</v>
       </c>
       <c r="N9">
-        <v>23.04120291066582</v>
+        <v>23.1789632322234</v>
       </c>
       <c r="O9">
-        <v>23.30971497746604</v>
+        <v>23.5017780996801</v>
       </c>
       <c r="P9">
-        <v>24.188661028109291</v>
+        <v>24.34887723415384</v>
       </c>
       <c r="Q9">
-        <v>24.617536262065979</v>
+        <v>24.82435995276465</v>
       </c>
       <c r="R9">
-        <v>25.14271088541231</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
+        <v>25.31395596960535</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>23.50961095524648</v>
+        <v>23.47163699863147</v>
       </c>
       <c r="C10">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D10">
-        <v>25.76746325714014</v>
-      </c>
-      <c r="E10" s="2">
-        <v>23.690558218456481</v>
+        <v>25.76083554910897</v>
+      </c>
+      <c r="E10">
+        <v>23.7322319048982</v>
       </c>
       <c r="F10">
-        <v>22.22432906260401</v>
+        <v>22.2809048808448</v>
       </c>
       <c r="G10">
-        <v>21.794762439524501</v>
+        <v>21.87029309239944</v>
       </c>
       <c r="H10">
-        <v>21.485871767201349</v>
+        <v>21.6142275639812</v>
       </c>
       <c r="I10">
-        <v>21.83733576952396</v>
+        <v>21.97449485060585</v>
       </c>
       <c r="J10">
-        <v>21.759687357574059</v>
+        <v>21.886262984302</v>
       </c>
       <c r="K10">
-        <v>21.964633312786621</v>
+        <v>22.09640952512181</v>
       </c>
       <c r="L10">
-        <v>22.448524446588991</v>
+        <v>22.6627632092852</v>
       </c>
       <c r="M10">
-        <v>22.809080825195409</v>
+        <v>23.02881120541415</v>
       </c>
       <c r="N10">
-        <v>22.86628602337554</v>
+        <v>23.04365911379156</v>
       </c>
       <c r="O10">
-        <v>23.16514085175131</v>
+        <v>23.35473207742593</v>
       </c>
       <c r="P10">
-        <v>24.042881219001639</v>
+        <v>24.23670951606664</v>
       </c>
       <c r="Q10">
-        <v>24.54451085894604</v>
+        <v>24.80076864372196</v>
       </c>
       <c r="R10">
-        <v>25.223255649369609</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>27</v>
+        <v>25.44689490386961</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>23.545509825346048</v>
+        <v>23.49204404893672</v>
       </c>
       <c r="C11">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D11">
-        <v>25.800672963590269</v>
-      </c>
-      <c r="E11" s="2">
-        <v>23.743457437546478</v>
+        <v>25.77177306819435</v>
+      </c>
+      <c r="E11">
+        <v>23.67023109429435</v>
       </c>
       <c r="F11">
-        <v>22.246146719482191</v>
+        <v>22.21003383833665</v>
       </c>
       <c r="G11">
-        <v>21.867934069540599</v>
+        <v>21.84557749756222</v>
       </c>
       <c r="H11">
-        <v>21.634008321754511</v>
+        <v>21.56438952988126</v>
       </c>
       <c r="I11">
-        <v>21.918199144726231</v>
+        <v>21.89938171511885</v>
       </c>
       <c r="J11">
-        <v>21.90773866951848</v>
+        <v>21.85284626699696</v>
       </c>
       <c r="K11">
-        <v>22.157013261228869</v>
+        <v>22.00594440795632</v>
       </c>
       <c r="L11">
-        <v>22.689786975157318</v>
+        <v>22.53911029349756</v>
       </c>
       <c r="M11">
-        <v>22.78875516804894</v>
+        <v>22.657102642175</v>
       </c>
       <c r="N11">
-        <v>22.68245264991511</v>
+        <v>22.63955681828047</v>
       </c>
       <c r="O11">
-        <v>22.946922767712621</v>
+        <v>22.86106996090964</v>
       </c>
       <c r="P11">
-        <v>23.83229250759025</v>
+        <v>23.72394573679263</v>
       </c>
       <c r="Q11">
-        <v>24.468906257658901</v>
+        <v>24.35863666409486</v>
       </c>
       <c r="R11">
-        <v>24.927510626153179</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>28</v>
+        <v>24.76059892360055</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>22.87493238486654</v>
+        <v>22.88304891629113</v>
       </c>
       <c r="C12">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D12">
-        <v>22.877742597994779</v>
+        <v>22.89700744565065</v>
       </c>
       <c r="E12">
-        <v>22.584810748038091</v>
+        <v>22.60157923288419</v>
       </c>
       <c r="F12">
-        <v>22.377731558046989</v>
+        <v>22.36990954474219</v>
       </c>
       <c r="G12">
-        <v>22.368866877915501</v>
+        <v>22.34741533722841</v>
       </c>
       <c r="H12">
-        <v>22.23760753052456</v>
+        <v>22.27320712257797</v>
       </c>
       <c r="I12">
-        <v>22.30407863084201</v>
+        <v>22.28145630259184</v>
       </c>
       <c r="J12">
-        <v>22.91124125450926</v>
+        <v>22.88827312335227</v>
       </c>
       <c r="K12">
-        <v>24.073254179664978</v>
+        <v>24.05371346133022</v>
       </c>
       <c r="L12">
-        <v>25.730729711592719</v>
+        <v>25.77243731338686</v>
       </c>
       <c r="M12">
-        <v>27.1070628028274</v>
+        <v>27.25405175591855</v>
       </c>
       <c r="N12">
-        <v>28.648447281070322</v>
+        <v>28.860632189161</v>
       </c>
       <c r="O12">
-        <v>29.254360704945491</v>
+        <v>29.45864253752315</v>
       </c>
       <c r="P12">
-        <v>29.125329110791331</v>
+        <v>29.28652664676022</v>
       </c>
       <c r="Q12">
-        <v>29.103145288913272</v>
+        <v>29.15260936891794</v>
       </c>
       <c r="R12">
-        <v>29.652562036967389</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
+        <v>29.70701160726849</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>22.98627449854812</v>
+        <v>23.00901520072983</v>
       </c>
       <c r="C13">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D13">
-        <v>22.98627449854812</v>
+        <v>22.99345687451578</v>
       </c>
       <c r="E13">
-        <v>23.047077801440281</v>
+        <v>23.09043247035899</v>
       </c>
       <c r="F13">
-        <v>22.75286390626956</v>
+        <v>22.72935286314836</v>
       </c>
       <c r="G13">
-        <v>22.32342761790424</v>
+        <v>22.40662325473617</v>
       </c>
       <c r="H13">
-        <v>23.60337886037038</v>
+        <v>23.55894469529022</v>
       </c>
       <c r="I13">
-        <v>24.032047102606409</v>
+        <v>24.09916932517081</v>
       </c>
       <c r="J13">
-        <v>24.12296771861584</v>
+        <v>24.12570763341241</v>
       </c>
       <c r="K13">
-        <v>24.511025650578521</v>
+        <v>24.49952459363621</v>
       </c>
       <c r="L13">
-        <v>26.361024330791661</v>
+        <v>26.37827172569118</v>
       </c>
       <c r="M13">
-        <v>28.02112207377137</v>
+        <v>27.98693603588389</v>
       </c>
       <c r="N13">
-        <v>28.524709951816899</v>
+        <v>28.5365199121314</v>
       </c>
       <c r="O13">
-        <v>28.67746607429514</v>
+        <v>28.56303224880342</v>
       </c>
       <c r="P13">
-        <v>29.184356448681619</v>
+        <v>29.08795354073128</v>
       </c>
       <c r="Q13">
-        <v>29.394843610445001</v>
+        <v>29.2182888038573</v>
       </c>
       <c r="R13">
-        <v>30.16273160921309</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
+        <v>29.98225553056636</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>23.37592386889958</v>
+        <v>23.42021443921109</v>
       </c>
       <c r="C14">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D14">
-        <v>27.580909856222171</v>
+        <v>27.60606589490132</v>
       </c>
       <c r="E14">
-        <v>23.612301633453662</v>
+        <v>23.64466095584059</v>
       </c>
       <c r="F14">
-        <v>22.16732154400653</v>
+        <v>22.26349513952713</v>
       </c>
       <c r="G14">
-        <v>21.872275423064369</v>
+        <v>21.97191101103775</v>
       </c>
       <c r="H14">
-        <v>21.847467934827112</v>
+        <v>21.94418793014658</v>
       </c>
       <c r="I14">
-        <v>21.645680555919451</v>
+        <v>21.51143818163562</v>
       </c>
       <c r="J14">
-        <v>21.85440307111341</v>
+        <v>21.87188628809542</v>
       </c>
       <c r="K14">
-        <v>21.75838680798099</v>
+        <v>21.75857472513464</v>
       </c>
       <c r="L14">
-        <v>21.878008261010219</v>
+        <v>21.90370462002536</v>
       </c>
       <c r="M14">
-        <v>22.272143926219272</v>
+        <v>22.30331961791545</v>
       </c>
       <c r="N14">
-        <v>22.404643660009839</v>
+        <v>22.4087906465057</v>
       </c>
       <c r="O14">
-        <v>22.965253699858462</v>
+        <v>23.13311734908687</v>
       </c>
       <c r="P14">
-        <v>23.691439718910789</v>
+        <v>23.91885706162042</v>
       </c>
       <c r="Q14">
-        <v>24.772375182356392</v>
+        <v>24.94812562043692</v>
       </c>
       <c r="R14">
-        <v>25.930756281528659</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
+        <v>26.21645496382816</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>23.363504665915169</v>
+        <v>23.41323295937379</v>
       </c>
       <c r="C15">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D15">
-        <v>27.604305387432561</v>
+        <v>27.59170027590058</v>
       </c>
       <c r="E15">
-        <v>23.6075602472194</v>
+        <v>23.59413662465715</v>
       </c>
       <c r="F15">
-        <v>22.16410548878731</v>
+        <v>22.21786788141292</v>
       </c>
       <c r="G15">
-        <v>21.905331343958309</v>
+        <v>21.97131201498312</v>
       </c>
       <c r="H15">
-        <v>21.898163718007488</v>
+        <v>21.92415320054153</v>
       </c>
       <c r="I15">
-        <v>21.51937055943359</v>
+        <v>21.68077781262449</v>
       </c>
       <c r="J15">
-        <v>21.789736322980961</v>
+        <v>21.87381079191639</v>
       </c>
       <c r="K15">
-        <v>21.671266246070601</v>
+        <v>21.7221236021629</v>
       </c>
       <c r="L15">
-        <v>21.811276140744749</v>
+        <v>21.68622426195142</v>
       </c>
       <c r="M15">
-        <v>22.162002056386559</v>
+        <v>22.13685262361262</v>
       </c>
       <c r="N15">
-        <v>22.276036673470319</v>
+        <v>22.27251032691699</v>
       </c>
       <c r="O15">
-        <v>22.936813295364111</v>
+        <v>22.93153936470334</v>
       </c>
       <c r="P15">
-        <v>23.817646495758162</v>
+        <v>23.87447966338266</v>
       </c>
       <c r="Q15">
-        <v>24.474844413764959</v>
+        <v>24.48465100593403</v>
       </c>
       <c r="R15">
-        <v>24.91908263245007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
+        <v>24.87294640495942</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>23.40275714289789</v>
+        <v>23.38569913701723</v>
       </c>
       <c r="C16">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D16">
-        <v>27.574477021890509</v>
+        <v>27.55013953430371</v>
       </c>
       <c r="E16">
-        <v>23.590421774981571</v>
+        <v>23.57626920252729</v>
       </c>
       <c r="F16">
-        <v>22.199195044994749</v>
+        <v>22.15158784839401</v>
       </c>
       <c r="G16">
-        <v>21.936176669402929</v>
+        <v>21.88742173820344</v>
       </c>
       <c r="H16">
-        <v>21.957669522522909</v>
+        <v>21.85556703820013</v>
       </c>
       <c r="I16">
-        <v>21.604531314861269</v>
+        <v>21.48473298142548</v>
       </c>
       <c r="J16">
-        <v>21.861382759720041</v>
+        <v>21.80813661634943</v>
       </c>
       <c r="K16">
-        <v>21.71798568899511</v>
+        <v>21.72594072811846</v>
       </c>
       <c r="L16">
-        <v>21.813510936691969</v>
+        <v>21.86229268593325</v>
       </c>
       <c r="M16">
-        <v>22.18142832918587</v>
+        <v>22.236299124814</v>
       </c>
       <c r="N16">
-        <v>22.34218393972915</v>
+        <v>22.35968841805719</v>
       </c>
       <c r="O16">
-        <v>23.216639475786561</v>
+        <v>23.27933794412284</v>
       </c>
       <c r="P16">
-        <v>24.304153354820599</v>
+        <v>24.38892326810109</v>
       </c>
       <c r="Q16">
-        <v>25.059595946523292</v>
+        <v>25.1722732278754</v>
       </c>
       <c r="R16">
-        <v>25.296303071038</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
+        <v>25.45765798310528</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>23.468391786644599</v>
+        <v>23.51267073655991</v>
       </c>
       <c r="C17">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D17">
-        <v>27.605228238445751</v>
+        <v>27.61975331949987</v>
       </c>
       <c r="E17">
-        <v>23.645850909548301</v>
+        <v>23.6145049643131</v>
       </c>
       <c r="F17">
-        <v>22.282116818243509</v>
+        <v>22.20936542526425</v>
       </c>
       <c r="G17">
-        <v>22.033314930443719</v>
+        <v>21.93797437188601</v>
       </c>
       <c r="H17">
-        <v>22.05592183569491</v>
+        <v>21.90046353852195</v>
       </c>
       <c r="I17">
-        <v>21.657420283201819</v>
+        <v>21.58546381954101</v>
       </c>
       <c r="J17">
-        <v>21.953249559419131</v>
+        <v>21.76249050031661</v>
       </c>
       <c r="K17">
-        <v>21.795791043902341</v>
+        <v>21.65854282711069</v>
       </c>
       <c r="L17">
-        <v>21.873989759440889</v>
+        <v>21.78464296283326</v>
       </c>
       <c r="M17">
-        <v>22.254703791388671</v>
+        <v>22.10938132253519</v>
       </c>
       <c r="N17">
-        <v>22.29308153453951</v>
+        <v>22.20434947739927</v>
       </c>
       <c r="O17">
-        <v>23.259183864278981</v>
+        <v>23.09612588883173</v>
       </c>
       <c r="P17">
-        <v>24.231732937855401</v>
+        <v>24.07303430913865</v>
       </c>
       <c r="Q17">
-        <v>25.047858459818141</v>
+        <v>24.95160860784868</v>
       </c>
       <c r="R17">
-        <v>25.25891826105606</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
+        <v>25.13242046733274</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>22.895668541049378</v>
+        <v>22.93002023258162</v>
       </c>
       <c r="C18">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D18">
-        <v>22.902840986732961</v>
+        <v>22.90516967387523</v>
       </c>
       <c r="E18">
-        <v>22.64570061612298</v>
+        <v>22.65972778016634</v>
       </c>
       <c r="F18">
-        <v>22.548383486289602</v>
+        <v>22.53516786912764</v>
       </c>
       <c r="G18">
-        <v>22.68788475038356</v>
+        <v>22.62887294912777</v>
       </c>
       <c r="H18">
-        <v>22.304708652427468</v>
+        <v>22.29499805086678</v>
       </c>
       <c r="I18">
-        <v>22.781156418619702</v>
+        <v>22.71265358093166</v>
       </c>
       <c r="J18">
-        <v>23.08036938149505</v>
+        <v>23.06402160834019</v>
       </c>
       <c r="K18">
-        <v>24.06327416170862</v>
+        <v>24.05604849232914</v>
       </c>
       <c r="L18">
-        <v>25.57344542808254</v>
+        <v>25.53244051187466</v>
       </c>
       <c r="M18">
-        <v>26.942536950611519</v>
+        <v>26.93647133749117</v>
       </c>
       <c r="N18">
-        <v>28.104054919761701</v>
+        <v>28.12088341926346</v>
       </c>
       <c r="O18">
-        <v>28.552169076795401</v>
+        <v>28.66611935089072</v>
       </c>
       <c r="P18">
-        <v>28.5514164035542</v>
+        <v>28.60670630005903</v>
       </c>
       <c r="Q18">
-        <v>28.445672136825429</v>
+        <v>28.54419198370611</v>
       </c>
       <c r="R18">
-        <v>28.37163500189391</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
+        <v>28.4958307833114</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>22.913528625594161</v>
+        <v>22.88617254897265</v>
       </c>
       <c r="C19">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D19">
-        <v>22.955050682869139</v>
+        <v>22.9430415393879</v>
       </c>
       <c r="E19">
-        <v>22.674238454993851</v>
+        <v>22.6793157246678</v>
       </c>
       <c r="F19">
-        <v>22.325907963424921</v>
+        <v>22.30516907960531</v>
       </c>
       <c r="G19">
-        <v>22.089790568325711</v>
+        <v>22.10655515757632</v>
       </c>
       <c r="H19">
-        <v>21.593357866065659</v>
+        <v>21.58192551259063</v>
       </c>
       <c r="I19">
-        <v>22.281327459871221</v>
+        <v>22.28802887224624</v>
       </c>
       <c r="J19">
-        <v>22.308137361929969</v>
+        <v>22.31018242922438</v>
       </c>
       <c r="K19">
-        <v>23.00535996840668</v>
+        <v>23.10108851053826</v>
       </c>
       <c r="L19">
-        <v>23.966396381818171</v>
+        <v>23.95846370923473</v>
       </c>
       <c r="M19">
-        <v>24.967212505410551</v>
+        <v>24.97324740068089</v>
       </c>
       <c r="N19">
-        <v>25.93181406000603</v>
+        <v>25.91170996561246</v>
       </c>
       <c r="O19">
-        <v>26.536534789754342</v>
+        <v>26.45919657665976</v>
       </c>
       <c r="P19">
-        <v>27.146713705415419</v>
+        <v>27.03156649998978</v>
       </c>
       <c r="Q19">
-        <v>27.458972748689028</v>
+        <v>27.28029391838836</v>
       </c>
       <c r="R19">
-        <v>27.828171721799819</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>36</v>
+        <v>27.72987483727537</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>22.977987940191131</v>
+        <v>22.97406102832392</v>
       </c>
       <c r="C20">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D20">
-        <v>22.98811556750217</v>
+        <v>22.96490732064066</v>
       </c>
       <c r="E20">
-        <v>22.58263402055384</v>
+        <v>22.51573262260802</v>
       </c>
       <c r="F20">
-        <v>21.973959203179</v>
+        <v>21.97081063064355</v>
       </c>
       <c r="G20">
-        <v>21.893171171392741</v>
+        <v>21.90573259404525</v>
       </c>
       <c r="H20">
-        <v>21.54786726116237</v>
+        <v>21.55522011534194</v>
       </c>
       <c r="I20">
-        <v>21.525985508238769</v>
+        <v>21.55098299062412</v>
       </c>
       <c r="J20">
-        <v>21.989511284954521</v>
+        <v>22.0239883648014</v>
       </c>
       <c r="K20">
-        <v>22.853058562862842</v>
+        <v>22.9210410251444</v>
       </c>
       <c r="L20">
-        <v>23.526837762315989</v>
+        <v>23.57048488950909</v>
       </c>
       <c r="M20">
-        <v>23.885102194814579</v>
+        <v>23.89414666110813</v>
       </c>
       <c r="N20">
-        <v>24.580389765980449</v>
+        <v>24.64305588180323</v>
       </c>
       <c r="O20">
-        <v>25.24603064253921</v>
+        <v>25.210933524989</v>
       </c>
       <c r="P20">
-        <v>25.414520478483809</v>
+        <v>25.3413645197961</v>
       </c>
       <c r="Q20">
-        <v>26.08620671189578</v>
+        <v>25.93297678088353</v>
       </c>
       <c r="R20">
-        <v>26.724052127090321</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>37</v>
+        <v>26.45152686799232</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>23.350428733708341</v>
+        <v>23.47506551945678</v>
       </c>
       <c r="C21">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D21">
-        <v>26.722516745880359</v>
+        <v>26.78942463160896</v>
       </c>
       <c r="E21">
-        <v>23.195619789440631</v>
+        <v>23.27975194712953</v>
       </c>
       <c r="F21">
-        <v>23.542424766842171</v>
+        <v>23.68551136539971</v>
       </c>
       <c r="G21">
-        <v>24.649623775235678</v>
+        <v>24.79598854105599</v>
       </c>
       <c r="H21">
-        <v>23.7567745610773</v>
+        <v>23.90445916029439</v>
       </c>
       <c r="I21">
-        <v>23.918531248805671</v>
+        <v>24.22428109623043</v>
       </c>
       <c r="J21">
-        <v>25.559344412737801</v>
+        <v>25.78591288719219</v>
       </c>
       <c r="K21">
-        <v>27.117049470124439</v>
+        <v>27.42094788180254</v>
       </c>
       <c r="L21">
-        <v>27.609674046624921</v>
+        <v>27.88834621851845</v>
       </c>
       <c r="M21">
-        <v>28.427384528309091</v>
+        <v>28.6913723288981</v>
       </c>
       <c r="N21">
-        <v>28.71514160911698</v>
+        <v>28.97248457623677</v>
       </c>
       <c r="O21">
-        <v>29.024836862819349</v>
+        <v>29.1629788123382</v>
       </c>
       <c r="P21">
-        <v>28.98039770540295</v>
+        <v>29.15534306742411</v>
       </c>
       <c r="Q21">
-        <v>28.854107568441119</v>
+        <v>28.98013743699961</v>
       </c>
       <c r="R21">
-        <v>29.269441273356492</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>38</v>
+        <v>29.35646368834329</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>23.388384424628281</v>
+        <v>23.41930943252927</v>
       </c>
       <c r="C22">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D22">
-        <v>26.797144236695441</v>
+        <v>26.81148537458581</v>
       </c>
       <c r="E22">
-        <v>23.240206403918929</v>
+        <v>23.26535551224678</v>
       </c>
       <c r="F22">
-        <v>23.52574871959354</v>
+        <v>23.62417904699555</v>
       </c>
       <c r="G22">
-        <v>24.64870050232598</v>
+        <v>24.89863637681983</v>
       </c>
       <c r="H22">
-        <v>23.811800945261179</v>
+        <v>23.81089272910262</v>
       </c>
       <c r="I22">
-        <v>23.734815784438851</v>
+        <v>23.7946602631421</v>
       </c>
       <c r="J22">
-        <v>25.542477703036951</v>
+        <v>25.53248809087905</v>
       </c>
       <c r="K22">
-        <v>27.062217703020899</v>
+        <v>26.94566064617943</v>
       </c>
       <c r="L22">
-        <v>27.850192724137202</v>
+        <v>27.71039427757603</v>
       </c>
       <c r="M22">
-        <v>28.1778098614882</v>
+        <v>28.09895045042226</v>
       </c>
       <c r="N22">
-        <v>28.666004042184401</v>
+        <v>28.73921587843889</v>
       </c>
       <c r="O22">
-        <v>28.75030732456138</v>
+        <v>28.82217457648393</v>
       </c>
       <c r="P22">
-        <v>28.480839182166392</v>
+        <v>28.71138884369403</v>
       </c>
       <c r="Q22">
-        <v>28.3743683022775</v>
+        <v>28.65798570068539</v>
       </c>
       <c r="R22">
-        <v>29.22006081714882</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>39</v>
+        <v>29.36832966913992</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>23.085787055029758</v>
+        <v>23.08224982213964</v>
       </c>
       <c r="C23">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D23">
-        <v>23.085787055029758</v>
+        <v>23.08224982213964</v>
       </c>
       <c r="E23">
-        <v>23.120254215300811</v>
+        <v>23.13723052455438</v>
       </c>
       <c r="F23">
-        <v>23.67247167773035</v>
+        <v>23.70027765998368</v>
       </c>
       <c r="G23">
-        <v>23.084954145372429</v>
+        <v>23.06154718274425</v>
       </c>
       <c r="H23">
-        <v>24.676975739039051</v>
+        <v>24.68783372707723</v>
       </c>
       <c r="I23">
-        <v>25.84291347777274</v>
+        <v>26.07134598977085</v>
       </c>
       <c r="J23">
-        <v>27.514641546883809</v>
+        <v>27.55295605841863</v>
       </c>
       <c r="K23">
-        <v>27.937589991814342</v>
+        <v>27.97418375021152</v>
       </c>
       <c r="L23">
-        <v>27.71144256993038</v>
+        <v>27.63461971491568</v>
       </c>
       <c r="M23">
-        <v>28.679336399675201</v>
+        <v>28.63561277880749</v>
       </c>
       <c r="N23">
-        <v>29.25205419839434</v>
+        <v>29.2169474568577</v>
       </c>
       <c r="O23">
-        <v>29.665519879720009</v>
+        <v>29.7355990302515</v>
       </c>
       <c r="P23">
-        <v>30.294382479351071</v>
+        <v>30.28575896325516</v>
       </c>
       <c r="Q23">
-        <v>30.534475991016851</v>
+        <v>30.540944329852</v>
       </c>
       <c r="R23">
-        <v>31.134334330864881</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>40</v>
+        <v>31.17797726601507</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>33.892769234453297</v>
+        <v>23.19619883619035</v>
       </c>
       <c r="C24">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D24">
-        <v>33.824850987447007</v>
+        <v>23.23124185629132</v>
       </c>
       <c r="E24">
-        <v>33.010923739069433</v>
+        <v>22.28736723990458</v>
       </c>
       <c r="F24">
-        <v>32.455265764754927</v>
+        <v>22.99235100395869</v>
       </c>
       <c r="G24">
-        <v>33.073526466382397</v>
+        <v>22.42993328764484</v>
       </c>
       <c r="H24">
-        <v>35.356711781383048</v>
+        <v>22.52876063669881</v>
       </c>
       <c r="I24">
-        <v>35.08595918085657</v>
+        <v>22.39615813574379</v>
       </c>
       <c r="J24">
-        <v>36.283117112930732</v>
+        <v>22.78753377233469</v>
       </c>
       <c r="K24">
-        <v>38.13379281391812</v>
+        <v>23.41548132489516</v>
       </c>
       <c r="L24">
-        <v>40.275515824758067</v>
+        <v>23.20689482244038</v>
       </c>
       <c r="M24">
-        <v>41.645685616851402</v>
+        <v>23.44891239329111</v>
       </c>
       <c r="N24">
-        <v>41.701467277986687</v>
+        <v>24.08722839111477</v>
       </c>
       <c r="O24">
-        <v>41.686230172734319</v>
+        <v>25.52479685392189</v>
       </c>
       <c r="P24">
-        <v>40.789943347214567</v>
+        <v>26.33302517587888</v>
       </c>
       <c r="Q24">
-        <v>40.262321791947151</v>
+        <v>27.86562119076055</v>
       </c>
       <c r="R24">
-        <v>40.322515056952838</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>41</v>
+        <v>29.31889164988896</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>34.552408292907607</v>
+        <v>23.10395055933318</v>
       </c>
       <c r="C25">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D25">
-        <v>34.430038395025129</v>
+        <v>23.12280978493632</v>
       </c>
       <c r="E25">
-        <v>33.964622854938668</v>
+        <v>22.18400502747989</v>
       </c>
       <c r="F25">
-        <v>33.871476751625799</v>
+        <v>22.91536405465557</v>
       </c>
       <c r="G25">
-        <v>33.526179815522433</v>
+        <v>22.38397926674374</v>
       </c>
       <c r="H25">
-        <v>33.759134919271908</v>
+        <v>22.69673782817375</v>
       </c>
       <c r="I25">
-        <v>35.735420374980841</v>
+        <v>23.30403114132656</v>
       </c>
       <c r="J25">
-        <v>37.918954345461252</v>
+        <v>24.10625017307588</v>
       </c>
       <c r="K25">
-        <v>40.333393195732818</v>
+        <v>23.96371938544476</v>
       </c>
       <c r="L25">
-        <v>42.819467585577463</v>
+        <v>23.83254692301788</v>
       </c>
       <c r="M25">
-        <v>44.705478654981277</v>
+        <v>23.55238790718725</v>
       </c>
       <c r="N25">
-        <v>46.688846446285119</v>
+        <v>24.07554523007822</v>
       </c>
       <c r="O25">
-        <v>48.537969149841267</v>
+        <v>24.86829506373262</v>
       </c>
       <c r="P25">
-        <v>49.536281643590762</v>
+        <v>26.02991059337381</v>
       </c>
       <c r="Q25">
-        <v>50.633393274680607</v>
+        <v>26.93872134565923</v>
       </c>
       <c r="R25">
-        <v>51.189897360868763</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>42</v>
+        <v>28.5320596847988</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>34.402134027824999</v>
+        <v>22.34732335293532</v>
       </c>
       <c r="C26">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D26">
-        <v>34.211853950345358</v>
+        <v>22.30135363148166</v>
       </c>
       <c r="E26">
-        <v>33.508394080031323</v>
+        <v>22.18520777390454</v>
       </c>
       <c r="F26">
-        <v>32.888418200084189</v>
+        <v>22.84748787328994</v>
       </c>
       <c r="G26">
-        <v>32.537870924819011</v>
+        <v>22.31813824171928</v>
       </c>
       <c r="H26">
-        <v>32.907428529858727</v>
+        <v>22.46450187150302</v>
       </c>
       <c r="I26">
-        <v>33.448003938787323</v>
+        <v>22.32223930888907</v>
       </c>
       <c r="J26">
-        <v>34.096346981961347</v>
+        <v>22.8144850894979</v>
       </c>
       <c r="K26">
-        <v>34.209064918976523</v>
+        <v>23.38720161484682</v>
       </c>
       <c r="L26">
-        <v>34.143323285091178</v>
+        <v>23.52703275077557</v>
       </c>
       <c r="M26">
-        <v>34.263148481815271</v>
+        <v>23.79993766257171</v>
       </c>
       <c r="N26">
-        <v>34.724672417583847</v>
+        <v>24.87009963453895</v>
       </c>
       <c r="O26">
-        <v>35.284255643712328</v>
+        <v>25.91282521422524</v>
       </c>
       <c r="P26">
-        <v>36.668152497001387</v>
+        <v>27.38298967897982</v>
       </c>
       <c r="Q26">
-        <v>36.767953020475467</v>
+        <v>28.7755955531026</v>
       </c>
       <c r="R26">
-        <v>37.488224664771167</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>43</v>
+        <v>31.06527910675134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>35.047130941101031</v>
+        <v>22.35215611247413</v>
       </c>
       <c r="C27">
-        <v>36.778325263510503</v>
+        <v>36.7783252635105</v>
       </c>
       <c r="D27">
-        <v>34.752145599364781</v>
+        <v>22.30157349617412</v>
       </c>
       <c r="E27">
-        <v>34.109685022615523</v>
+        <v>22.20382682607948</v>
       </c>
       <c r="F27">
-        <v>33.001138259245479</v>
+        <v>22.82371420737601</v>
       </c>
       <c r="G27">
-        <v>32.068705753012637</v>
+        <v>22.32558878389974</v>
       </c>
       <c r="H27">
-        <v>32.747522464974018</v>
+        <v>22.39579638144877</v>
       </c>
       <c r="I27">
-        <v>34.072368851519691</v>
+        <v>22.28071497695999</v>
       </c>
       <c r="J27">
-        <v>34.557912769438502</v>
+        <v>22.44632122782164</v>
       </c>
       <c r="K27">
-        <v>34.964967828374178</v>
+        <v>22.64181031463891</v>
       </c>
       <c r="L27">
-        <v>35.247872441862079</v>
+        <v>22.41260910898866</v>
       </c>
       <c r="M27">
-        <v>35.410598725401833</v>
+        <v>22.19892778959036</v>
       </c>
       <c r="N27">
-        <v>35.837898547659179</v>
+        <v>22.32572332286126</v>
       </c>
       <c r="O27">
-        <v>36.982160985577188</v>
+        <v>22.79559559298269</v>
       </c>
       <c r="P27">
-        <v>37.861873541492301</v>
+        <v>23.70103606515718</v>
       </c>
       <c r="Q27">
-        <v>39.414876467334622</v>
+        <v>23.90856473092141</v>
       </c>
       <c r="R27">
-        <v>40.807439151777267</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>44</v>
+        <v>25.92836574983927</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>23.163462450724531</v>
+        <v>23.07811272382682</v>
       </c>
       <c r="C28">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D28" s="2">
-        <v>23.211250047975</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D28">
+        <v>23.10292601458669</v>
       </c>
       <c r="E28">
-        <v>22.266649396964439</v>
+        <v>22.1687958457596</v>
       </c>
       <c r="F28">
-        <v>22.954358059083329</v>
+        <v>22.9393670277166</v>
       </c>
       <c r="G28">
-        <v>22.418546285953759</v>
+        <v>22.38905495748809</v>
       </c>
       <c r="H28">
-        <v>22.5021189867511</v>
+        <v>22.72166480884211</v>
       </c>
       <c r="I28">
-        <v>22.341916664225</v>
+        <v>23.20396690573278</v>
       </c>
       <c r="J28">
-        <v>22.87339119311978</v>
+        <v>23.76232632467745</v>
       </c>
       <c r="K28">
-        <v>23.418316882235018</v>
+        <v>23.3289563897113</v>
       </c>
       <c r="L28">
-        <v>23.192855500835108</v>
+        <v>23.27091926680697</v>
       </c>
       <c r="M28">
-        <v>23.409089447304979</v>
+        <v>22.78431922951665</v>
       </c>
       <c r="N28">
-        <v>23.997050357392361</v>
+        <v>22.92552880978287</v>
       </c>
       <c r="O28">
-        <v>25.305218396851519</v>
+        <v>23.32494634071239</v>
       </c>
       <c r="P28">
-        <v>26.161685506728631</v>
+        <v>24.18126527045981</v>
       </c>
       <c r="Q28">
-        <v>27.599308430758018</v>
+        <v>24.37153268814858</v>
       </c>
       <c r="R28">
-        <v>28.96180006069379</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>45</v>
+        <v>25.40301731063927</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>23.0117541265165</v>
+        <v>23.12422564763277</v>
       </c>
       <c r="C29">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D29" s="2">
-        <v>23.081196173332469</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D29">
+        <v>23.13766284948791</v>
       </c>
       <c r="E29">
-        <v>22.151311774761311</v>
+        <v>22.18571822545039</v>
       </c>
       <c r="F29">
-        <v>22.88648850867639</v>
+        <v>22.93685022581949</v>
       </c>
       <c r="G29">
-        <v>22.330034188640688</v>
+        <v>22.43330731262206</v>
       </c>
       <c r="H29">
-        <v>22.671031290249338</v>
+        <v>22.72690337820855</v>
       </c>
       <c r="I29">
-        <v>23.30030888998348</v>
+        <v>23.18210005271328</v>
       </c>
       <c r="J29">
-        <v>24.164768841378681</v>
+        <v>23.70975639300849</v>
       </c>
       <c r="K29">
-        <v>23.819912606042369</v>
+        <v>23.3897865198733</v>
       </c>
       <c r="L29">
-        <v>24.04510538144357</v>
+        <v>23.36429361901686</v>
       </c>
       <c r="M29">
-        <v>23.673282220396889</v>
+        <v>22.87334430703193</v>
       </c>
       <c r="N29">
-        <v>24.351696426497121</v>
+        <v>22.9376666297534</v>
       </c>
       <c r="O29">
-        <v>25.200424336548569</v>
+        <v>23.17392487504033</v>
       </c>
       <c r="P29">
-        <v>26.445917718431211</v>
+        <v>23.94148146813928</v>
       </c>
       <c r="Q29">
-        <v>27.43292612242935</v>
+        <v>24.00216824627586</v>
       </c>
       <c r="R29">
-        <v>28.992427297876571</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>46</v>
+        <v>25.03222995658892</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>22.3788635713852</v>
+        <v>23.0949280630902</v>
       </c>
       <c r="C30">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D30" s="2">
-        <v>22.306285454222039</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D30">
+        <v>23.12499079161933</v>
       </c>
       <c r="E30">
-        <v>22.166945795337181</v>
+        <v>22.17598302064018</v>
       </c>
       <c r="F30">
-        <v>22.731589188084911</v>
+        <v>22.8763139492545</v>
       </c>
       <c r="G30">
-        <v>22.26643402070744</v>
+        <v>22.29354175663261</v>
       </c>
       <c r="H30">
-        <v>22.36034557879394</v>
+        <v>22.58634690526145</v>
       </c>
       <c r="I30">
-        <v>22.319105695827218</v>
+        <v>23.00029828461168</v>
       </c>
       <c r="J30">
-        <v>22.75581179723325</v>
+        <v>23.46013340826243</v>
       </c>
       <c r="K30">
-        <v>23.441997091037351</v>
+        <v>23.02558710729859</v>
       </c>
       <c r="L30">
-        <v>23.480336884308709</v>
+        <v>22.97821584141129</v>
       </c>
       <c r="M30">
-        <v>23.721537230454501</v>
+        <v>22.64324094785929</v>
       </c>
       <c r="N30">
-        <v>24.659934018729501</v>
+        <v>22.65983730378849</v>
       </c>
       <c r="O30">
-        <v>25.75651940085956</v>
+        <v>22.81797456001067</v>
       </c>
       <c r="P30">
-        <v>27.207807577571408</v>
+        <v>23.52283342498921</v>
       </c>
       <c r="Q30">
-        <v>28.521565737528949</v>
+        <v>23.62076552206172</v>
       </c>
       <c r="R30">
-        <v>30.78080843118617</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>47</v>
+        <v>24.54161534551639</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>22.340127365159969</v>
+        <v>23.0635181857057</v>
       </c>
       <c r="C31">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D31" s="2">
-        <v>22.288008009199832</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D31">
+        <v>23.09237591335621</v>
       </c>
       <c r="E31">
-        <v>22.158638682610199</v>
+        <v>22.13641969773129</v>
       </c>
       <c r="F31">
-        <v>22.731085507962121</v>
+        <v>22.84213397951406</v>
       </c>
       <c r="G31">
-        <v>22.272919490822069</v>
+        <v>22.35797457435601</v>
       </c>
       <c r="H31">
-        <v>22.388180731271529</v>
+        <v>22.61439931449411</v>
       </c>
       <c r="I31">
-        <v>22.219158205326881</v>
+        <v>23.05998065341845</v>
       </c>
       <c r="J31">
-        <v>22.37487109147532</v>
+        <v>23.47874864140958</v>
       </c>
       <c r="K31">
-        <v>22.572682342576289</v>
+        <v>23.20341358959199</v>
       </c>
       <c r="L31">
-        <v>22.416888771883279</v>
+        <v>23.25443432846832</v>
       </c>
       <c r="M31">
-        <v>22.096676903239569</v>
+        <v>22.7124263137454</v>
       </c>
       <c r="N31">
-        <v>22.212693254531811</v>
+        <v>22.74481465153961</v>
       </c>
       <c r="O31">
-        <v>22.734196334988351</v>
+        <v>22.86179272575597</v>
       </c>
       <c r="P31">
-        <v>23.686895905412388</v>
+        <v>23.45975811741462</v>
       </c>
       <c r="Q31">
-        <v>23.776966137875728</v>
+        <v>23.62884271489524</v>
       </c>
       <c r="R31">
-        <v>25.77935041222706</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>48</v>
+        <v>24.14774686402687</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>23.062868980475191</v>
+        <v>23.06855621589696</v>
       </c>
       <c r="C32">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D32" s="2">
-        <v>23.12003199874691</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D32">
+        <v>23.09873993538283</v>
       </c>
       <c r="E32">
-        <v>22.190026417136082</v>
+        <v>22.19014988899618</v>
       </c>
       <c r="F32">
-        <v>22.951141902359598</v>
+        <v>23.01337275266835</v>
       </c>
       <c r="G32">
-        <v>22.380062626919621</v>
+        <v>22.42049522585699</v>
       </c>
       <c r="H32">
-        <v>22.652854526024921</v>
+        <v>22.74127926170976</v>
       </c>
       <c r="I32">
-        <v>23.074485807820061</v>
+        <v>23.30233699698508</v>
       </c>
       <c r="J32">
-        <v>23.631752268694129</v>
+        <v>23.80630375014221</v>
       </c>
       <c r="K32">
-        <v>23.159276166781481</v>
+        <v>23.58064092585175</v>
       </c>
       <c r="L32">
-        <v>23.10546695830331</v>
+        <v>23.4235504592998</v>
       </c>
       <c r="M32">
-        <v>22.750098896695441</v>
+        <v>22.85693124874779</v>
       </c>
       <c r="N32">
-        <v>22.886575629816392</v>
+        <v>22.98295032666232</v>
       </c>
       <c r="O32">
-        <v>23.157637945966439</v>
+        <v>23.49517116439174</v>
       </c>
       <c r="P32">
-        <v>24.01316972756058</v>
+        <v>24.30234390766749</v>
       </c>
       <c r="Q32">
-        <v>24.30104148591743</v>
+        <v>24.21938255778832</v>
       </c>
       <c r="R32">
-        <v>25.272295774222702</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>49</v>
+        <v>24.98349557619063</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>23.13871665756276</v>
+        <v>23.01204755393896</v>
       </c>
       <c r="C33">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D33" s="2">
-        <v>23.137928354373361</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D33">
+        <v>23.09382497248628</v>
       </c>
       <c r="E33">
-        <v>22.160160602654351</v>
+        <v>22.16579144199038</v>
       </c>
       <c r="F33">
-        <v>22.889835862765981</v>
+        <v>22.86854122785586</v>
       </c>
       <c r="G33">
-        <v>22.399514707440972</v>
+        <v>22.36528517677571</v>
       </c>
       <c r="H33">
-        <v>22.685731229775101</v>
+        <v>22.6697582314455</v>
       </c>
       <c r="I33">
-        <v>23.1795433636319</v>
+        <v>23.22410828784336</v>
       </c>
       <c r="J33">
-        <v>23.656668806044081</v>
+        <v>23.79670428185826</v>
       </c>
       <c r="K33">
-        <v>23.370479736917499</v>
+        <v>23.44443042050235</v>
       </c>
       <c r="L33">
-        <v>23.329617350977831</v>
+        <v>23.24492700441487</v>
       </c>
       <c r="M33">
-        <v>22.776989897908461</v>
+        <v>22.69360688862349</v>
       </c>
       <c r="N33">
-        <v>22.79048887458184</v>
+        <v>22.73110454276448</v>
       </c>
       <c r="O33">
-        <v>23.047676434639971</v>
+        <v>23.1487383750432</v>
       </c>
       <c r="P33">
-        <v>23.83420132566896</v>
+        <v>23.92063030946403</v>
       </c>
       <c r="Q33">
-        <v>23.970165505624859</v>
+        <v>23.93296415029109</v>
       </c>
       <c r="R33">
-        <v>24.906280324272341</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>50</v>
+        <v>24.6099725833843</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>23.105959369936031</v>
+        <v>23.09130738232558</v>
       </c>
       <c r="C34">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D34" s="2">
-        <v>23.15927873301845</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D34">
+        <v>23.14385577721444</v>
       </c>
       <c r="E34">
-        <v>22.234376936940748</v>
+        <v>22.20066653686231</v>
       </c>
       <c r="F34">
-        <v>23.00780012775229</v>
+        <v>22.97827799673806</v>
       </c>
       <c r="G34">
-        <v>22.542754446499679</v>
+        <v>22.43045238265405</v>
       </c>
       <c r="H34">
-        <v>22.81185204439657</v>
+        <v>22.72927109464134</v>
       </c>
       <c r="I34">
-        <v>23.27043858822756</v>
+        <v>23.14413429725808</v>
       </c>
       <c r="J34">
-        <v>23.749706988854101</v>
+        <v>23.67992236945596</v>
       </c>
       <c r="K34">
-        <v>23.390005970871272</v>
+        <v>23.33379985110889</v>
       </c>
       <c r="L34">
-        <v>23.25688204082148</v>
+        <v>23.22175405843157</v>
       </c>
       <c r="M34">
-        <v>22.833895301465908</v>
+        <v>22.61865561990444</v>
       </c>
       <c r="N34">
-        <v>22.814749904382101</v>
+        <v>22.77387379872762</v>
       </c>
       <c r="O34">
-        <v>23.084673866401619</v>
+        <v>23.19296065383396</v>
       </c>
       <c r="P34">
-        <v>23.7178520249035</v>
+        <v>23.89387665850223</v>
       </c>
       <c r="Q34">
-        <v>23.834816718368991</v>
+        <v>23.76754305592666</v>
       </c>
       <c r="R34">
-        <v>24.643728224356931</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>51</v>
+        <v>24.53339379730529</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>23.078815924057771</v>
+        <v>23.05344953484236</v>
       </c>
       <c r="C35">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D35" s="2">
-        <v>23.137124159871959</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D35">
+        <v>23.09273363324128</v>
       </c>
       <c r="E35">
-        <v>22.169500492672231</v>
+        <v>22.13753534048172</v>
       </c>
       <c r="F35">
-        <v>22.880459533439812</v>
+        <v>22.8349445490784</v>
       </c>
       <c r="G35">
-        <v>22.385426794106799</v>
+        <v>22.36823806508183</v>
       </c>
       <c r="H35">
-        <v>22.69490848306846</v>
+        <v>22.61175697591824</v>
       </c>
       <c r="I35">
-        <v>23.22573114644624</v>
+        <v>23.076131509712</v>
       </c>
       <c r="J35">
-        <v>23.68318734193733</v>
+        <v>23.4903603366733</v>
       </c>
       <c r="K35">
-        <v>23.330004409626181</v>
+        <v>23.20518528306718</v>
       </c>
       <c r="L35">
-        <v>23.34267337620437</v>
+        <v>23.24232059243287</v>
       </c>
       <c r="M35">
-        <v>22.822170380588769</v>
+        <v>22.69347945702233</v>
       </c>
       <c r="N35">
-        <v>22.863549337800009</v>
+        <v>22.72303875456901</v>
       </c>
       <c r="O35">
-        <v>22.922284851044751</v>
+        <v>23.02511173313541</v>
       </c>
       <c r="P35">
-        <v>23.498550082080879</v>
+        <v>23.7318639833714</v>
       </c>
       <c r="Q35">
-        <v>23.598886633010341</v>
+        <v>23.64715092019183</v>
       </c>
       <c r="R35">
-        <v>24.199146071540479</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>52</v>
+        <v>24.28788501507309</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>23.121949138326482</v>
+        <v>23.0608733011215</v>
       </c>
       <c r="C36">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D36" s="2">
-        <v>23.123017550362061</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D36">
+        <v>23.11954846358823</v>
       </c>
       <c r="E36">
-        <v>22.176105272933949</v>
+        <v>22.15690426308864</v>
       </c>
       <c r="F36">
-        <v>22.870742669042141</v>
+        <v>22.90270575526258</v>
       </c>
       <c r="G36">
-        <v>22.350147871499448</v>
+        <v>22.39984136577718</v>
       </c>
       <c r="H36">
-        <v>22.63715656955867</v>
+        <v>22.65919051897293</v>
       </c>
       <c r="I36">
-        <v>23.048183920390031</v>
+        <v>23.11785662991304</v>
       </c>
       <c r="J36">
-        <v>23.609571174613009</v>
+        <v>23.65515659834846</v>
       </c>
       <c r="K36">
-        <v>23.299449189778219</v>
+        <v>23.30796053739882</v>
       </c>
       <c r="L36">
-        <v>23.347697412367339</v>
+        <v>23.24987827071127</v>
       </c>
       <c r="M36">
-        <v>22.730021152173912</v>
+        <v>22.75017540475999</v>
       </c>
       <c r="N36">
-        <v>22.837817590751349</v>
+        <v>22.82311484085613</v>
       </c>
       <c r="O36">
-        <v>23.28060263935668</v>
+        <v>22.87765131376776</v>
       </c>
       <c r="P36">
-        <v>24.102900707410829</v>
+        <v>23.54915873367149</v>
       </c>
       <c r="Q36">
-        <v>23.997526427891259</v>
+        <v>23.59714156663345</v>
       </c>
       <c r="R36">
-        <v>24.82260732727487</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>53</v>
+        <v>24.03462809012567</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>23.120618530900622</v>
+        <v>22.10393742808749</v>
       </c>
       <c r="C37">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D37" s="2">
-        <v>23.10562317759819</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D37">
+        <v>22.10393742808749</v>
       </c>
       <c r="E37">
-        <v>22.1655537018177</v>
+        <v>22.1663888486286</v>
       </c>
       <c r="F37">
-        <v>22.871878489529301</v>
+        <v>22.18031607616891</v>
       </c>
       <c r="G37">
-        <v>22.358544653530959</v>
+        <v>22.21612206879708</v>
       </c>
       <c r="H37">
-        <v>22.630880584456879</v>
+        <v>23.10877302248595</v>
       </c>
       <c r="I37">
-        <v>23.084181373368398</v>
+        <v>23.89751555269296</v>
       </c>
       <c r="J37">
-        <v>23.608075279594321</v>
+        <v>23.43411622497721</v>
       </c>
       <c r="K37">
-        <v>23.22286666046919</v>
+        <v>23.74122354505201</v>
       </c>
       <c r="L37">
-        <v>23.170662474817519</v>
+        <v>24.09345367917906</v>
       </c>
       <c r="M37">
-        <v>22.602978441730119</v>
+        <v>25.04340009920627</v>
       </c>
       <c r="N37">
-        <v>22.797305913464619</v>
+        <v>26.22389431220714</v>
       </c>
       <c r="O37">
-        <v>23.072430137546199</v>
+        <v>27.67808743736451</v>
       </c>
       <c r="P37">
-        <v>23.774021456329741</v>
+        <v>29.70058004907724</v>
       </c>
       <c r="Q37">
-        <v>23.721682940968179</v>
+        <v>30.93459908890777</v>
       </c>
       <c r="R37">
-        <v>24.34633063832575</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>54</v>
+        <v>32.08987709176358</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>23.079331955717919</v>
+        <v>22.23215319271402</v>
       </c>
       <c r="C38">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D38" s="2">
-        <v>23.108305773972329</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D38">
+        <v>22.21336832122952</v>
       </c>
       <c r="E38">
-        <v>22.162481838614379</v>
+        <v>22.17668523443627</v>
       </c>
       <c r="F38">
-        <v>22.842132160710449</v>
+        <v>22.09647526464956</v>
       </c>
       <c r="G38">
-        <v>22.365118253981649</v>
+        <v>22.08427348267199</v>
       </c>
       <c r="H38">
-        <v>22.67165571101858</v>
+        <v>22.52052886247612</v>
       </c>
       <c r="I38">
-        <v>23.165165724137019</v>
+        <v>23.00887686894284</v>
       </c>
       <c r="J38">
-        <v>23.67417646404407</v>
+        <v>23.06005852233731</v>
       </c>
       <c r="K38">
-        <v>23.272304024036789</v>
+        <v>23.84738695502346</v>
       </c>
       <c r="L38">
-        <v>23.138300570887569</v>
+        <v>25.49003816192742</v>
       </c>
       <c r="M38">
-        <v>22.533904131052729</v>
+        <v>26.20359534947436</v>
       </c>
       <c r="N38">
-        <v>22.595436878454489</v>
+        <v>26.51943438616479</v>
       </c>
       <c r="O38">
-        <v>22.93918853301934</v>
+        <v>25.9865480000763</v>
       </c>
       <c r="P38">
-        <v>23.690189910579011</v>
+        <v>25.52771206862847</v>
       </c>
       <c r="Q38">
-        <v>23.532931852840559</v>
+        <v>26.02314667278941</v>
       </c>
       <c r="R38">
-        <v>24.19650719605491</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>55</v>
+        <v>26.56163101974402</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>23.034499956042161</v>
+        <v>22.26706264125324</v>
       </c>
       <c r="C39">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D39" s="2">
-        <v>23.12791361923183</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D39">
+        <v>22.19889393183644</v>
       </c>
       <c r="E39">
-        <v>22.188188111773531</v>
+        <v>22.20897384202701</v>
       </c>
       <c r="F39">
-        <v>22.936982288375869</v>
+        <v>22.0830585136105</v>
       </c>
       <c r="G39">
-        <v>22.406561908741121</v>
+        <v>22.11365606231145</v>
       </c>
       <c r="H39">
-        <v>22.687666523834309</v>
+        <v>22.53470242727872</v>
       </c>
       <c r="I39">
-        <v>23.165177378747881</v>
+        <v>22.94781539556352</v>
       </c>
       <c r="J39">
-        <v>23.733413226924931</v>
+        <v>22.6006244576922</v>
       </c>
       <c r="K39">
-        <v>23.449400835814089</v>
+        <v>23.11285152115039</v>
       </c>
       <c r="L39">
-        <v>23.353018716034601</v>
+        <v>25.11370787950299</v>
       </c>
       <c r="M39">
-        <v>22.696508275382261</v>
+        <v>25.69204040406584</v>
       </c>
       <c r="N39">
-        <v>22.78542878379946</v>
+        <v>26.03864697760438</v>
       </c>
       <c r="O39">
-        <v>23.282946254653009</v>
+        <v>26.2134940584765</v>
       </c>
       <c r="P39">
-        <v>23.922762714771601</v>
+        <v>26.17786053146744</v>
       </c>
       <c r="Q39">
-        <v>23.851750378961011</v>
+        <v>26.20205390017057</v>
       </c>
       <c r="R39">
-        <v>24.432212608845049</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>56</v>
+        <v>27.14795566004147</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>23.06619191833267</v>
+        <v>23.4079131814763</v>
       </c>
       <c r="C40">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D40" s="2">
-        <v>23.088729718591559</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D40">
+        <v>23.22905148159902</v>
       </c>
       <c r="E40">
-        <v>22.176765161508701</v>
+        <v>23.44885894529377</v>
       </c>
       <c r="F40">
-        <v>23.023313167807409</v>
+        <v>23.89396757822901</v>
       </c>
       <c r="G40">
-        <v>22.47994624885424</v>
+        <v>22.94928918825111</v>
       </c>
       <c r="H40">
-        <v>22.744254812536859</v>
+        <v>22.42719525672033</v>
       </c>
       <c r="I40">
-        <v>23.175812498172071</v>
+        <v>23.24623132458421</v>
       </c>
       <c r="J40">
-        <v>23.646996560973069</v>
+        <v>24.28943689014853</v>
       </c>
       <c r="K40">
-        <v>23.265836178205461</v>
+        <v>25.17663121409698</v>
       </c>
       <c r="L40">
-        <v>23.336567838388</v>
+        <v>25.66329195775386</v>
       </c>
       <c r="M40">
-        <v>22.811683830249759</v>
+        <v>26.21332004065749</v>
       </c>
       <c r="N40">
-        <v>22.819052124430101</v>
+        <v>27.25224568783856</v>
       </c>
       <c r="O40">
-        <v>22.95547892555188</v>
+        <v>29.18368978238489</v>
       </c>
       <c r="P40">
-        <v>23.49642228606108</v>
+        <v>31.42216677871811</v>
       </c>
       <c r="Q40">
-        <v>23.55671237781463</v>
+        <v>33.43621416102988</v>
       </c>
       <c r="R40">
-        <v>23.962813030960771</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>57</v>
+        <v>34.42567943712844</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>22.14037477804478</v>
+        <v>23.4511212046266</v>
       </c>
       <c r="C41">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D41" s="2">
-        <v>22.134720271781749</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D41">
+        <v>23.4511212046266</v>
       </c>
       <c r="E41">
-        <v>22.127905090540601</v>
+        <v>22.71667281731481</v>
       </c>
       <c r="F41">
-        <v>22.131385384072431</v>
+        <v>24.35678332323823</v>
       </c>
       <c r="G41">
-        <v>22.215493053972718</v>
+        <v>24.56411763070299</v>
       </c>
       <c r="H41">
-        <v>23.09457222642294</v>
+        <v>24.2469203737808</v>
       </c>
       <c r="I41">
-        <v>23.938388877010961</v>
+        <v>25.54518770789621</v>
       </c>
       <c r="J41">
-        <v>23.46068210089738</v>
+        <v>25.84249731590164</v>
       </c>
       <c r="K41">
-        <v>23.80392016173149</v>
+        <v>26.00556685615377</v>
       </c>
       <c r="L41">
-        <v>24.26486679648913</v>
+        <v>26.67722601777638</v>
       </c>
       <c r="M41">
-        <v>25.13107953761703</v>
+        <v>27.49129475123706</v>
       </c>
       <c r="N41">
-        <v>26.25112215412064</v>
+        <v>28.75411500128819</v>
       </c>
       <c r="O41">
-        <v>27.707716330672461</v>
+        <v>30.85795166708219</v>
       </c>
       <c r="P41">
-        <v>29.791135741204961</v>
+        <v>31.66502699671733</v>
       </c>
       <c r="Q41">
-        <v>31.019847977445341</v>
+        <v>32.48741327160942</v>
       </c>
       <c r="R41">
-        <v>32.222963733551403</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>58</v>
+        <v>33.03649388619452</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>22.210476549271039</v>
+        <v>22.89133441265551</v>
       </c>
       <c r="C42">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D42" s="2">
-        <v>22.18121386875832</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D42">
+        <v>26.73247845769018</v>
       </c>
       <c r="E42">
-        <v>22.134500245393209</v>
+        <v>22.74894564340975</v>
       </c>
       <c r="F42">
-        <v>22.158563590047809</v>
+        <v>23.82196585209693</v>
       </c>
       <c r="G42">
-        <v>22.118311550663631</v>
+        <v>25.21121173360656</v>
       </c>
       <c r="H42">
-        <v>22.52741553963499</v>
+        <v>24.60869523423765</v>
       </c>
       <c r="I42">
-        <v>22.96138975221043</v>
+        <v>24.16453103198456</v>
       </c>
       <c r="J42">
-        <v>23.005404762469631</v>
+        <v>24.69287891798501</v>
       </c>
       <c r="K42">
-        <v>23.903691930746511</v>
+        <v>26.32009800361815</v>
       </c>
       <c r="L42">
-        <v>25.58378267508748</v>
+        <v>27.9968191173394</v>
       </c>
       <c r="M42">
-        <v>26.318226376317529</v>
+        <v>29.07998822257478</v>
       </c>
       <c r="N42">
-        <v>26.607223292450509</v>
+        <v>29.98350243608951</v>
       </c>
       <c r="O42">
-        <v>26.02433125938391</v>
+        <v>30.5411100833722</v>
       </c>
       <c r="P42">
-        <v>25.59304590346531</v>
+        <v>31.08511648032851</v>
       </c>
       <c r="Q42">
-        <v>26.150960596309051</v>
+        <v>32.02943613560208</v>
       </c>
       <c r="R42">
-        <v>26.66028130971468</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>59</v>
+        <v>33.04277862508632</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>22.153459114107719</v>
+        <v>22.69975939451975</v>
       </c>
       <c r="C43">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D43" s="2">
-        <v>22.140646350376851</v>
+        <v>36.7783252635105</v>
+      </c>
+      <c r="D43">
+        <v>22.68082301985628</v>
       </c>
       <c r="E43">
-        <v>22.069410720928349</v>
+        <v>23.10884236761735</v>
       </c>
       <c r="F43">
-        <v>22.040414073089551</v>
+        <v>23.49929784307953</v>
       </c>
       <c r="G43">
-        <v>22.060503426201709</v>
+        <v>23.2754481981239</v>
       </c>
       <c r="H43">
-        <v>22.473458714452491</v>
+        <v>24.43665044720631</v>
       </c>
       <c r="I43">
-        <v>22.844871449384151</v>
+        <v>24.53316526377354</v>
       </c>
       <c r="J43">
-        <v>22.506722991016549</v>
+        <v>25.23350918494233</v>
       </c>
       <c r="K43">
-        <v>23.037675833855051</v>
+        <v>25.76698196765998</v>
       </c>
       <c r="L43">
-        <v>24.978171176229601</v>
+        <v>26.80709707526522</v>
       </c>
       <c r="M43">
-        <v>25.517412218001649</v>
+        <v>28.23290723267012</v>
       </c>
       <c r="N43">
-        <v>25.937715718441311</v>
+        <v>29.60552968977899</v>
       </c>
       <c r="O43">
-        <v>26.013978569334711</v>
+        <v>30.7043944664307</v>
       </c>
       <c r="P43">
-        <v>25.920767628401322</v>
+        <v>31.10324955762805</v>
       </c>
       <c r="Q43">
-        <v>25.937643797662449</v>
+        <v>31.18145538853662</v>
       </c>
       <c r="R43">
-        <v>26.98217519100028</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44">
-        <v>23.475289450272079</v>
-      </c>
-      <c r="C44">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D44" s="2">
-        <v>23.237291851189411</v>
-      </c>
-      <c r="E44">
-        <v>23.372116853213068</v>
-      </c>
-      <c r="F44">
-        <v>23.769794812187431</v>
-      </c>
-      <c r="G44">
-        <v>22.800726405646309</v>
-      </c>
-      <c r="H44">
-        <v>22.381179621394761</v>
-      </c>
-      <c r="I44">
-        <v>23.067056036533771</v>
-      </c>
-      <c r="J44">
-        <v>24.023821357313281</v>
-      </c>
-      <c r="K44">
-        <v>24.938701912292309</v>
-      </c>
-      <c r="L44">
-        <v>25.458550613004029</v>
-      </c>
-      <c r="M44">
-        <v>26.02498598176609</v>
-      </c>
-      <c r="N44">
-        <v>27.076061632489949</v>
-      </c>
-      <c r="O44">
-        <v>28.84800957705643</v>
-      </c>
-      <c r="P44">
-        <v>31.048117970959101</v>
-      </c>
-      <c r="Q44">
-        <v>32.924221879598747</v>
-      </c>
-      <c r="R44">
-        <v>33.885228784444351</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45">
-        <v>23.48137694321461</v>
-      </c>
-      <c r="C45">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D45">
-        <v>23.48137694321461</v>
-      </c>
-      <c r="E45">
-        <v>22.79085458081364</v>
-      </c>
-      <c r="F45">
-        <v>24.444536873452119</v>
-      </c>
-      <c r="G45">
-        <v>24.631518633595238</v>
-      </c>
-      <c r="H45">
-        <v>24.268756917305829</v>
-      </c>
-      <c r="I45">
-        <v>25.38047490515908</v>
-      </c>
-      <c r="J45">
-        <v>25.70574013255672</v>
-      </c>
-      <c r="K45">
-        <v>26.026620540133891</v>
-      </c>
-      <c r="L45">
-        <v>26.71069233759685</v>
-      </c>
-      <c r="M45">
-        <v>27.429773933397751</v>
-      </c>
-      <c r="N45">
-        <v>28.70740351692519</v>
-      </c>
-      <c r="O45">
-        <v>30.738712048828159</v>
-      </c>
-      <c r="P45">
-        <v>31.53593629873653</v>
-      </c>
-      <c r="Q45">
-        <v>32.410079960364293</v>
-      </c>
-      <c r="R45">
-        <v>33.017744157005268</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46">
-        <v>22.798919668199861</v>
-      </c>
-      <c r="C46">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D46">
-        <v>26.708765672529019</v>
-      </c>
-      <c r="E46" s="2">
-        <v>22.775768706961301</v>
-      </c>
-      <c r="F46">
-        <v>23.870788732580358</v>
-      </c>
-      <c r="G46">
-        <v>25.307411509349201</v>
-      </c>
-      <c r="H46">
-        <v>24.795876393602121</v>
-      </c>
-      <c r="I46">
-        <v>24.214033259838779</v>
-      </c>
-      <c r="J46">
-        <v>24.71201627251088</v>
-      </c>
-      <c r="K46">
-        <v>26.41247652760341</v>
-      </c>
-      <c r="L46">
-        <v>28.024583041745231</v>
-      </c>
-      <c r="M46">
-        <v>29.121157804746979</v>
-      </c>
-      <c r="N46">
-        <v>30.15964936035741</v>
-      </c>
-      <c r="O46">
-        <v>30.644856638157972</v>
-      </c>
-      <c r="P46">
-        <v>31.176424245856769</v>
-      </c>
-      <c r="Q46">
-        <v>32.170679616360168</v>
-      </c>
-      <c r="R46">
-        <v>33.139741880308627</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47">
-        <v>22.68759852640321</v>
-      </c>
-      <c r="C47">
-        <v>36.778325263510503</v>
-      </c>
-      <c r="D47">
-        <v>22.687598526403221</v>
-      </c>
-      <c r="E47">
-        <v>23.125797059178812</v>
-      </c>
-      <c r="F47">
-        <v>23.489124532847619</v>
-      </c>
-      <c r="G47">
-        <v>23.233899592958711</v>
-      </c>
-      <c r="H47">
-        <v>24.335401725174439</v>
-      </c>
-      <c r="I47">
-        <v>24.479720303008889</v>
-      </c>
-      <c r="J47">
-        <v>25.084873979295171</v>
-      </c>
-      <c r="K47">
-        <v>25.66625676063763</v>
-      </c>
-      <c r="L47">
-        <v>26.623985492304289</v>
-      </c>
-      <c r="M47">
-        <v>28.020076758863809</v>
-      </c>
-      <c r="N47">
-        <v>29.495048445414071</v>
-      </c>
-      <c r="O47">
-        <v>30.493431291058631</v>
-      </c>
-      <c r="P47">
-        <v>30.88837615192768</v>
-      </c>
-      <c r="Q47">
-        <v>30.963411252419469</v>
-      </c>
-      <c r="R47">
-        <v>31.363552726914278</v>
+        <v>31.5341403794124</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:R47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>